--- a/artfynd/A 6929-2026 artfynd.xlsx
+++ b/artfynd/A 6929-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131752909</v>
+        <v>131752957</v>
       </c>
       <c r="B2" t="n">
-        <v>57898</v>
+        <v>91849</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,29 +686,24 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>496478</v>
+        <v>496342</v>
       </c>
       <c r="R2" t="n">
-        <v>7036088</v>
+        <v>7036007</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,17 +751,13 @@
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -805,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131752950</v>
+        <v>131752909</v>
       </c>
       <c r="B3" t="n">
-        <v>80365</v>
+        <v>57899</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,26 +807,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -843,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496205</v>
+        <v>496478</v>
       </c>
       <c r="R3" t="n">
-        <v>7035804</v>
+        <v>7036088</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,13 +877,17 @@
           <t>2026-03-18</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -898,22 +898,17 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -931,10 +926,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131752957</v>
+        <v>131752901</v>
       </c>
       <c r="B4" t="n">
-        <v>91848</v>
+        <v>57899</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -942,24 +937,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -969,10 +969,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496342</v>
+        <v>496305</v>
       </c>
       <c r="R4" t="n">
-        <v>7036007</v>
+        <v>7036020</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,13 +1007,17 @@
           <t>2026-03-18</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1032,9 +1036,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1052,10 +1061,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131752901</v>
+        <v>131752950</v>
       </c>
       <c r="B5" t="n">
-        <v>57898</v>
+        <v>80366</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,31 +1072,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1095,10 +1099,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>496305</v>
+        <v>496205</v>
       </c>
       <c r="R5" t="n">
-        <v>7036020</v>
+        <v>7035804</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1133,17 +1137,13 @@
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1154,22 +1154,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1187,10 +1187,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131752891</v>
+        <v>131752962</v>
       </c>
       <c r="B6" t="n">
-        <v>91828</v>
+        <v>79261</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,30 +1198,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1229,10 +1225,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496242</v>
+        <v>496528</v>
       </c>
       <c r="R6" t="n">
-        <v>7035834</v>
+        <v>7036197</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1312,10 +1308,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131752962</v>
+        <v>131752891</v>
       </c>
       <c r="B7" t="n">
-        <v>79260</v>
+        <v>91829</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,26 +1319,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496528</v>
+        <v>496242</v>
       </c>
       <c r="R7" t="n">
-        <v>7036197</v>
+        <v>7035834</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1433,10 +1433,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131752915</v>
+        <v>131752918</v>
       </c>
       <c r="B8" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,10 +1476,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496426</v>
+        <v>496408</v>
       </c>
       <c r="R8" t="n">
-        <v>7036022</v>
+        <v>7036004</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1568,10 +1568,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131752914</v>
+        <v>131752915</v>
       </c>
       <c r="B9" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496424</v>
+        <v>496426</v>
       </c>
       <c r="R9" t="n">
-        <v>7036021</v>
+        <v>7036022</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1678,9 +1678,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1698,10 +1703,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131752918</v>
+        <v>131752914</v>
       </c>
       <c r="B10" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1741,10 +1746,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>496408</v>
+        <v>496424</v>
       </c>
       <c r="R10" t="n">
-        <v>7036004</v>
+        <v>7036021</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1808,14 +1813,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1833,10 +1833,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131752963</v>
+        <v>131752924</v>
       </c>
       <c r="B11" t="n">
-        <v>79260</v>
+        <v>57899</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1844,26 +1844,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1871,10 +1876,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>496243</v>
+        <v>496209</v>
       </c>
       <c r="R11" t="n">
-        <v>7035811</v>
+        <v>7035774</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1911,7 +1916,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1920,7 +1925,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1939,9 +1943,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1959,10 +1968,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131752924</v>
+        <v>131752910</v>
       </c>
       <c r="B12" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1992,7 +2001,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2002,10 +2011,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>496209</v>
+        <v>496471</v>
       </c>
       <c r="R12" t="n">
-        <v>7035774</v>
+        <v>7036080</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2042,7 +2051,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2069,14 +2078,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2094,10 +2098,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131752910</v>
+        <v>131752963</v>
       </c>
       <c r="B13" t="n">
-        <v>57898</v>
+        <v>79261</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2105,31 +2109,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2137,10 +2136,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>496471</v>
+        <v>496243</v>
       </c>
       <c r="R13" t="n">
-        <v>7036080</v>
+        <v>7035811</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2177,7 +2176,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2186,6 +2185,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2227,7 +2227,7 @@
         <v>131752913</v>
       </c>
       <c r="B14" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>131752923</v>
       </c>
       <c r="B15" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2484,10 +2484,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131752887</v>
+        <v>131752956</v>
       </c>
       <c r="B16" t="n">
-        <v>83240</v>
+        <v>91849</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2495,26 +2495,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2522,10 +2522,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>496531</v>
+        <v>496130</v>
       </c>
       <c r="R16" t="n">
-        <v>7036184</v>
+        <v>7035766</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2608,7 +2608,7 @@
         <v>131752905</v>
       </c>
       <c r="B17" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2735,10 +2735,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131752903</v>
+        <v>131752887</v>
       </c>
       <c r="B18" t="n">
-        <v>57898</v>
+        <v>83241</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2746,31 +2746,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2778,10 +2773,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496454</v>
+        <v>496531</v>
       </c>
       <c r="R18" t="n">
-        <v>7036201</v>
+        <v>7036184</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2816,17 +2811,13 @@
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2868,7 +2859,7 @@
         <v>131752943</v>
       </c>
       <c r="B19" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2986,10 +2977,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131752956</v>
+        <v>131752903</v>
       </c>
       <c r="B20" t="n">
-        <v>91848</v>
+        <v>57899</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2997,24 +2988,29 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3024,10 +3020,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>496130</v>
+        <v>496454</v>
       </c>
       <c r="R20" t="n">
-        <v>7035766</v>
+        <v>7036201</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3062,13 +3058,17 @@
           <t>2026-03-18</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3107,10 +3107,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131752920</v>
+        <v>131752955</v>
       </c>
       <c r="B21" t="n">
-        <v>57898</v>
+        <v>91825</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3118,29 +3118,28 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3150,10 +3149,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>496360</v>
+        <v>496475</v>
       </c>
       <c r="R21" t="n">
-        <v>7035948</v>
+        <v>7036170</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3188,17 +3187,13 @@
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3237,10 +3232,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131752955</v>
+        <v>131752920</v>
       </c>
       <c r="B22" t="n">
-        <v>91824</v>
+        <v>57899</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3248,28 +3243,29 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3279,10 +3275,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496475</v>
+        <v>496360</v>
       </c>
       <c r="R22" t="n">
-        <v>7036170</v>
+        <v>7035948</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3317,13 +3313,17 @@
           <t>2026-03-18</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3362,10 +3362,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131752898</v>
+        <v>131752942</v>
       </c>
       <c r="B23" t="n">
-        <v>57898</v>
+        <v>80367</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3373,31 +3373,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3405,10 +3400,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496293</v>
+        <v>496194</v>
       </c>
       <c r="R23" t="n">
-        <v>7035984</v>
+        <v>7035755</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3443,17 +3438,13 @@
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3464,22 +3455,17 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3497,10 +3483,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131752907</v>
+        <v>131752898</v>
       </c>
       <c r="B24" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3530,7 +3516,7 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3540,10 +3526,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>496513</v>
+        <v>496293</v>
       </c>
       <c r="R24" t="n">
-        <v>7036129</v>
+        <v>7035984</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3580,7 +3566,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3607,9 +3593,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3627,10 +3618,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131752942</v>
+        <v>131752907</v>
       </c>
       <c r="B25" t="n">
-        <v>80366</v>
+        <v>57899</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3638,26 +3629,31 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3665,10 +3661,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>496194</v>
+        <v>496513</v>
       </c>
       <c r="R25" t="n">
-        <v>7035755</v>
+        <v>7036129</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3703,13 +3699,17 @@
           <t>2026-03-18</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3720,17 +3720,17 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3748,10 +3748,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131752961</v>
+        <v>131752919</v>
       </c>
       <c r="B26" t="n">
-        <v>79260</v>
+        <v>57899</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3759,26 +3759,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3786,10 +3791,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>496271</v>
+        <v>496379</v>
       </c>
       <c r="R26" t="n">
-        <v>7035921</v>
+        <v>7035973</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3826,7 +3831,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3835,7 +3840,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3854,9 +3858,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3874,10 +3883,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131752919</v>
+        <v>131752961</v>
       </c>
       <c r="B27" t="n">
-        <v>57898</v>
+        <v>79261</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3885,31 +3894,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3917,10 +3921,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>496379</v>
+        <v>496271</v>
       </c>
       <c r="R27" t="n">
-        <v>7035973</v>
+        <v>7035921</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3957,7 +3961,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3966,6 +3970,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3984,14 +3989,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4009,10 +4009,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131752900</v>
+        <v>131752917</v>
       </c>
       <c r="B28" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4052,10 +4052,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>496293</v>
+        <v>496409</v>
       </c>
       <c r="R28" t="n">
-        <v>7035993</v>
+        <v>7036004</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4147,7 +4147,7 @@
         <v>131752906</v>
       </c>
       <c r="B29" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>131752908</v>
       </c>
       <c r="B30" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4404,10 +4404,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131752917</v>
+        <v>131752897</v>
       </c>
       <c r="B31" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4447,10 +4447,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>496409</v>
+        <v>496304</v>
       </c>
       <c r="R31" t="n">
-        <v>7036004</v>
+        <v>7035979</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4539,39 +4539,40 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131752890</v>
+        <v>131752900</v>
       </c>
       <c r="B32" t="n">
-        <v>91791</v>
+        <v>57899</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -4581,10 +4582,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>496286</v>
+        <v>496293</v>
       </c>
       <c r="R32" t="n">
-        <v>7035879</v>
+        <v>7035993</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4619,13 +4620,17 @@
           <t>2026-03-18</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4644,9 +4649,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4664,40 +4674,39 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131752897</v>
+        <v>131752890</v>
       </c>
       <c r="B33" t="n">
-        <v>57898</v>
+        <v>91792</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4707,10 +4716,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>496304</v>
+        <v>496286</v>
       </c>
       <c r="R33" t="n">
-        <v>7035979</v>
+        <v>7035879</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4745,17 +4754,13 @@
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4774,14 +4779,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4799,10 +4799,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131752911</v>
+        <v>131752922</v>
       </c>
       <c r="B34" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4842,10 +4842,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>496472</v>
+        <v>496323</v>
       </c>
       <c r="R34" t="n">
-        <v>7036081</v>
+        <v>7035905</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4882,7 +4882,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4909,14 +4909,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4934,10 +4929,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131752922</v>
+        <v>131752911</v>
       </c>
       <c r="B35" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4967,7 +4962,7 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -4977,10 +4972,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>496323</v>
+        <v>496472</v>
       </c>
       <c r="R35" t="n">
-        <v>7035905</v>
+        <v>7036081</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5017,7 +5012,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5044,9 +5039,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5067,7 +5067,7 @@
         <v>131752949</v>
       </c>
       <c r="B36" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>131752953</v>
       </c>
       <c r="B37" t="n">
-        <v>78272</v>
+        <v>78273</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5311,10 +5311,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131752896</v>
+        <v>131752939</v>
       </c>
       <c r="B38" t="n">
-        <v>57898</v>
+        <v>80367</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5322,31 +5322,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -5354,10 +5349,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>496249</v>
+        <v>496130</v>
       </c>
       <c r="R38" t="n">
-        <v>7035881</v>
+        <v>7035728</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5392,17 +5387,13 @@
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en tall.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5413,17 +5404,22 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5441,10 +5437,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131752944</v>
+        <v>131752896</v>
       </c>
       <c r="B39" t="n">
-        <v>80365</v>
+        <v>57899</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5452,26 +5448,31 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5479,10 +5480,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>496246</v>
+        <v>496249</v>
       </c>
       <c r="R39" t="n">
-        <v>7035859</v>
+        <v>7035881</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5517,13 +5518,17 @@
           <t>2026-03-18</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en tall.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5534,17 +5539,17 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5562,7 +5567,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131752939</v>
+        <v>131752944</v>
       </c>
       <c r="B40" t="n">
         <v>80366</v>
@@ -5573,21 +5578,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5600,10 +5605,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>496130</v>
+        <v>496246</v>
       </c>
       <c r="R40" t="n">
-        <v>7035728</v>
+        <v>7035859</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5663,14 +5668,9 @@
           <t>Salix caprea</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5691,7 +5691,7 @@
         <v>131752912</v>
       </c>
       <c r="B41" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5821,7 +5821,7 @@
         <v>131752902</v>
       </c>
       <c r="B42" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5953,10 +5953,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131752958</v>
+        <v>131752941</v>
       </c>
       <c r="B43" t="n">
-        <v>91848</v>
+        <v>80367</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5964,26 +5964,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5991,10 +5991,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>496359</v>
+        <v>496195</v>
       </c>
       <c r="R43" t="n">
-        <v>7035980</v>
+        <v>7035791</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6046,17 +6046,22 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6074,10 +6079,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131752941</v>
+        <v>131752958</v>
       </c>
       <c r="B44" t="n">
-        <v>80366</v>
+        <v>91849</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6085,26 +6090,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -6112,10 +6117,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>496195</v>
+        <v>496359</v>
       </c>
       <c r="R44" t="n">
-        <v>7035791</v>
+        <v>7035980</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6167,22 +6172,17 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6203,7 +6203,7 @@
         <v>131752952</v>
       </c>
       <c r="B45" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6326,10 +6326,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131752938</v>
+        <v>131752947</v>
       </c>
       <c r="B46" t="n">
-        <v>57898</v>
+        <v>80366</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6337,31 +6337,26 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6369,10 +6364,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>496294</v>
+        <v>496215</v>
       </c>
       <c r="R46" t="n">
-        <v>7035996</v>
+        <v>7035808</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6407,17 +6402,13 @@
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6428,22 +6419,22 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6461,10 +6452,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131752947</v>
+        <v>131752916</v>
       </c>
       <c r="B47" t="n">
-        <v>80365</v>
+        <v>57899</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6472,26 +6463,31 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6499,10 +6495,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>496215</v>
+        <v>496424</v>
       </c>
       <c r="R47" t="n">
-        <v>7035808</v>
+        <v>7036028</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6537,13 +6533,17 @@
           <t>2026-03-18</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6554,22 +6554,17 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6590,7 +6585,7 @@
         <v>131752946</v>
       </c>
       <c r="B48" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6708,10 +6703,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131752916</v>
+        <v>131752938</v>
       </c>
       <c r="B49" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6741,7 +6736,7 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -6751,10 +6746,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>496424</v>
+        <v>496294</v>
       </c>
       <c r="R49" t="n">
-        <v>7036028</v>
+        <v>7035996</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6791,7 +6786,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6818,9 +6813,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6841,7 +6841,7 @@
         <v>131752945</v>
       </c>
       <c r="B50" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6962,7 +6962,7 @@
         <v>131752940</v>
       </c>
       <c r="B51" t="n">
-        <v>80366</v>
+        <v>80367</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7080,10 +7080,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131752904</v>
+        <v>131752951</v>
       </c>
       <c r="B52" t="n">
-        <v>57898</v>
+        <v>80366</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7091,31 +7091,26 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -7123,10 +7118,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>496441</v>
+        <v>496223</v>
       </c>
       <c r="R52" t="n">
-        <v>7036179</v>
+        <v>7035781</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7161,17 +7156,13 @@
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -7182,22 +7173,17 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7215,10 +7201,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131752951</v>
+        <v>131752904</v>
       </c>
       <c r="B53" t="n">
-        <v>80365</v>
+        <v>57899</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7226,26 +7212,31 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -7253,10 +7244,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>496223</v>
+        <v>496441</v>
       </c>
       <c r="R53" t="n">
-        <v>7035781</v>
+        <v>7036179</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7291,13 +7282,17 @@
           <t>2026-03-18</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -7308,17 +7303,22 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>

--- a/artfynd/A 6929-2026 artfynd.xlsx
+++ b/artfynd/A 6929-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131752957</v>
       </c>
       <c r="B2" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131752909</v>
+        <v>131752950</v>
       </c>
       <c r="B3" t="n">
-        <v>57899</v>
+        <v>80369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,31 +807,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -839,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496478</v>
+        <v>496205</v>
       </c>
       <c r="R3" t="n">
-        <v>7036088</v>
+        <v>7035804</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,17 +872,13 @@
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -898,17 +889,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -926,10 +922,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131752901</v>
+        <v>131752909</v>
       </c>
       <c r="B4" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -959,7 +955,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -969,10 +965,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496305</v>
+        <v>496478</v>
       </c>
       <c r="R4" t="n">
-        <v>7036020</v>
+        <v>7036088</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,7 +1005,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,14 +1032,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1061,10 +1052,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131752950</v>
+        <v>131752901</v>
       </c>
       <c r="B5" t="n">
-        <v>80366</v>
+        <v>57902</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1072,26 +1063,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1099,10 +1095,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>496205</v>
+        <v>496305</v>
       </c>
       <c r="R5" t="n">
-        <v>7035804</v>
+        <v>7036020</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1137,13 +1133,17 @@
           <t>2026-03-18</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1154,22 +1154,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1187,10 +1187,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131752962</v>
+        <v>131752891</v>
       </c>
       <c r="B6" t="n">
-        <v>79261</v>
+        <v>91832</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,26 +1198,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1225,10 +1229,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496528</v>
+        <v>496242</v>
       </c>
       <c r="R6" t="n">
-        <v>7036197</v>
+        <v>7035834</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1308,10 +1312,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131752891</v>
+        <v>131752962</v>
       </c>
       <c r="B7" t="n">
-        <v>91829</v>
+        <v>79264</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,30 +1323,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496242</v>
+        <v>496528</v>
       </c>
       <c r="R7" t="n">
-        <v>7035834</v>
+        <v>7036197</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1436,7 +1436,7 @@
         <v>131752918</v>
       </c>
       <c r="B8" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>131752915</v>
       </c>
       <c r="B9" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>131752914</v>
       </c>
       <c r="B10" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>131752924</v>
       </c>
       <c r="B11" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>131752910</v>
       </c>
       <c r="B12" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>131752963</v>
       </c>
       <c r="B13" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>131752913</v>
       </c>
       <c r="B14" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>131752923</v>
       </c>
       <c r="B15" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2484,10 +2484,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131752956</v>
+        <v>131752887</v>
       </c>
       <c r="B16" t="n">
-        <v>91849</v>
+        <v>83244</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2495,26 +2495,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2522,10 +2522,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>496130</v>
+        <v>496531</v>
       </c>
       <c r="R16" t="n">
-        <v>7035766</v>
+        <v>7036184</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2608,7 +2608,7 @@
         <v>131752905</v>
       </c>
       <c r="B17" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2735,10 +2735,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131752887</v>
+        <v>131752903</v>
       </c>
       <c r="B18" t="n">
-        <v>83241</v>
+        <v>57902</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2746,26 +2746,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2773,10 +2778,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496531</v>
+        <v>496454</v>
       </c>
       <c r="R18" t="n">
-        <v>7036184</v>
+        <v>7036201</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2811,13 +2816,17 @@
           <t>2026-03-18</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2856,10 +2865,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131752943</v>
+        <v>131752956</v>
       </c>
       <c r="B19" t="n">
-        <v>80366</v>
+        <v>91852</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2867,26 +2876,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2894,10 +2903,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>496214</v>
+        <v>496130</v>
       </c>
       <c r="R19" t="n">
-        <v>7035803</v>
+        <v>7035766</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2977,10 +2986,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131752903</v>
+        <v>131752943</v>
       </c>
       <c r="B20" t="n">
-        <v>57899</v>
+        <v>80369</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2988,31 +2997,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3020,10 +3024,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>496454</v>
+        <v>496214</v>
       </c>
       <c r="R20" t="n">
-        <v>7036201</v>
+        <v>7035803</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3058,17 +3062,13 @@
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3110,7 +3110,7 @@
         <v>131752955</v>
       </c>
       <c r="B21" t="n">
-        <v>91825</v>
+        <v>91828</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>131752920</v>
       </c>
       <c r="B22" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         <v>131752942</v>
       </c>
       <c r="B23" t="n">
-        <v>80367</v>
+        <v>80370</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>131752898</v>
       </c>
       <c r="B24" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>131752907</v>
       </c>
       <c r="B25" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>131752919</v>
       </c>
       <c r="B26" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>131752961</v>
       </c>
       <c r="B27" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4009,40 +4009,39 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131752917</v>
+        <v>131752890</v>
       </c>
       <c r="B28" t="n">
-        <v>57899</v>
+        <v>91795</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -4052,10 +4051,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>496409</v>
+        <v>496286</v>
       </c>
       <c r="R28" t="n">
-        <v>7036004</v>
+        <v>7035879</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4090,17 +4089,13 @@
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4119,14 +4114,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4144,10 +4134,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131752906</v>
+        <v>131752917</v>
       </c>
       <c r="B29" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4177,7 +4167,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4187,10 +4177,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>496475</v>
+        <v>496409</v>
       </c>
       <c r="R29" t="n">
-        <v>7036177</v>
+        <v>7036004</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4227,7 +4217,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4254,9 +4244,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4274,10 +4269,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131752908</v>
+        <v>131752906</v>
       </c>
       <c r="B30" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4317,10 +4312,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>496506</v>
+        <v>496475</v>
       </c>
       <c r="R30" t="n">
-        <v>7036124</v>
+        <v>7036177</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4404,10 +4399,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131752897</v>
+        <v>131752908</v>
       </c>
       <c r="B31" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4437,7 +4432,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4447,10 +4442,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>496304</v>
+        <v>496506</v>
       </c>
       <c r="R31" t="n">
-        <v>7035979</v>
+        <v>7036124</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4487,7 +4482,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4514,14 +4509,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4539,10 +4529,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131752900</v>
+        <v>131752897</v>
       </c>
       <c r="B32" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4582,10 +4572,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>496293</v>
+        <v>496304</v>
       </c>
       <c r="R32" t="n">
-        <v>7035993</v>
+        <v>7035979</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4674,39 +4664,40 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131752890</v>
+        <v>131752900</v>
       </c>
       <c r="B33" t="n">
-        <v>91792</v>
+        <v>57902</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4716,10 +4707,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>496286</v>
+        <v>496293</v>
       </c>
       <c r="R33" t="n">
-        <v>7035879</v>
+        <v>7035993</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4754,13 +4745,17 @@
           <t>2026-03-18</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4779,9 +4774,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4802,7 +4802,7 @@
         <v>131752922</v>
       </c>
       <c r="B34" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>131752911</v>
       </c>
       <c r="B35" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>131752949</v>
       </c>
       <c r="B36" t="n">
-        <v>80366</v>
+        <v>80369</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>131752953</v>
       </c>
       <c r="B37" t="n">
-        <v>78273</v>
+        <v>78276</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5311,10 +5311,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131752939</v>
+        <v>131752896</v>
       </c>
       <c r="B38" t="n">
-        <v>80367</v>
+        <v>57902</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5322,26 +5322,31 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -5349,10 +5354,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>496130</v>
+        <v>496249</v>
       </c>
       <c r="R38" t="n">
-        <v>7035728</v>
+        <v>7035881</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5387,13 +5392,17 @@
           <t>2026-03-18</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en tall.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5404,22 +5413,17 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5437,10 +5441,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131752896</v>
+        <v>131752939</v>
       </c>
       <c r="B39" t="n">
-        <v>57899</v>
+        <v>80370</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5448,31 +5452,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5480,10 +5479,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>496249</v>
+        <v>496130</v>
       </c>
       <c r="R39" t="n">
-        <v>7035881</v>
+        <v>7035728</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5518,17 +5517,13 @@
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en tall.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5539,17 +5534,22 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5570,7 +5570,7 @@
         <v>131752944</v>
       </c>
       <c r="B40" t="n">
-        <v>80366</v>
+        <v>80369</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>131752912</v>
       </c>
       <c r="B41" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5821,7 +5821,7 @@
         <v>131752902</v>
       </c>
       <c r="B42" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5953,10 +5953,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131752941</v>
+        <v>131752958</v>
       </c>
       <c r="B43" t="n">
-        <v>80367</v>
+        <v>91852</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5964,26 +5964,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5991,10 +5991,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>496195</v>
+        <v>496359</v>
       </c>
       <c r="R43" t="n">
-        <v>7035791</v>
+        <v>7035980</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6046,22 +6046,17 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6079,10 +6074,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131752958</v>
+        <v>131752941</v>
       </c>
       <c r="B44" t="n">
-        <v>91849</v>
+        <v>80370</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6090,26 +6085,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -6117,10 +6112,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>496359</v>
+        <v>496195</v>
       </c>
       <c r="R44" t="n">
-        <v>7035980</v>
+        <v>7035791</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6172,17 +6167,22 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6200,10 +6200,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131752952</v>
+        <v>131752916</v>
       </c>
       <c r="B45" t="n">
-        <v>80366</v>
+        <v>57902</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6211,26 +6211,31 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6238,10 +6243,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>496192</v>
+        <v>496424</v>
       </c>
       <c r="R45" t="n">
-        <v>7035762</v>
+        <v>7036028</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6276,13 +6281,17 @@
           <t>2026-03-18</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6293,22 +6302,17 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6326,10 +6330,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131752947</v>
+        <v>131752938</v>
       </c>
       <c r="B46" t="n">
-        <v>80366</v>
+        <v>57902</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6337,26 +6341,31 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6364,10 +6373,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>496215</v>
+        <v>496294</v>
       </c>
       <c r="R46" t="n">
-        <v>7035808</v>
+        <v>7035996</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6402,13 +6411,17 @@
           <t>2026-03-18</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6419,22 +6432,22 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6452,10 +6465,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131752916</v>
+        <v>131752952</v>
       </c>
       <c r="B47" t="n">
-        <v>57899</v>
+        <v>80369</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6463,31 +6476,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6495,10 +6503,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>496424</v>
+        <v>496192</v>
       </c>
       <c r="R47" t="n">
-        <v>7036028</v>
+        <v>7035762</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6533,17 +6541,13 @@
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6554,17 +6558,22 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6582,10 +6591,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131752946</v>
+        <v>131752947</v>
       </c>
       <c r="B48" t="n">
-        <v>80366</v>
+        <v>80369</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6620,10 +6629,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>496218</v>
+        <v>496215</v>
       </c>
       <c r="R48" t="n">
-        <v>7035789</v>
+        <v>7035808</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6675,17 +6684,22 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6703,10 +6717,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131752938</v>
+        <v>131752946</v>
       </c>
       <c r="B49" t="n">
-        <v>57899</v>
+        <v>80369</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6714,31 +6728,26 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6746,10 +6755,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>496294</v>
+        <v>496218</v>
       </c>
       <c r="R49" t="n">
-        <v>7035996</v>
+        <v>7035789</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6784,17 +6793,13 @@
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6805,22 +6810,17 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6838,10 +6838,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131752945</v>
+        <v>131752940</v>
       </c>
       <c r="B50" t="n">
-        <v>80366</v>
+        <v>80370</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6849,21 +6849,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6876,10 +6876,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>496358</v>
+        <v>496212</v>
       </c>
       <c r="R50" t="n">
-        <v>7035946</v>
+        <v>7035799</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6959,10 +6959,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131752940</v>
+        <v>131752945</v>
       </c>
       <c r="B51" t="n">
-        <v>80367</v>
+        <v>80369</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6970,21 +6970,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6997,10 +6997,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>496212</v>
+        <v>496358</v>
       </c>
       <c r="R51" t="n">
-        <v>7035799</v>
+        <v>7035946</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7083,7 +7083,7 @@
         <v>131752951</v>
       </c>
       <c r="B52" t="n">
-        <v>80366</v>
+        <v>80369</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>131752904</v>
       </c>
       <c r="B53" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 6929-2026 artfynd.xlsx
+++ b/artfynd/A 6929-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131752957</v>
+        <v>131752909</v>
       </c>
       <c r="B2" t="n">
-        <v>91852</v>
+        <v>57902</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,24 +686,29 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -713,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>496342</v>
+        <v>496478</v>
       </c>
       <c r="R2" t="n">
-        <v>7036007</v>
+        <v>7036088</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,13 +756,17 @@
           <t>2026-03-18</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -796,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131752950</v>
+        <v>131752901</v>
       </c>
       <c r="B3" t="n">
-        <v>80369</v>
+        <v>57902</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,26 +816,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +848,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496205</v>
+        <v>496305</v>
       </c>
       <c r="R3" t="n">
-        <v>7035804</v>
+        <v>7036020</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,13 +886,17 @@
           <t>2026-03-18</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -889,22 +907,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -922,10 +940,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131752909</v>
+        <v>131752957</v>
       </c>
       <c r="B4" t="n">
-        <v>57902</v>
+        <v>91852</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,29 +951,24 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -965,10 +978,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496478</v>
+        <v>496342</v>
       </c>
       <c r="R4" t="n">
-        <v>7036088</v>
+        <v>7036007</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,17 +1016,13 @@
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1052,10 +1061,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131752901</v>
+        <v>131752950</v>
       </c>
       <c r="B5" t="n">
-        <v>57902</v>
+        <v>80369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,31 +1072,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1095,10 +1099,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>496305</v>
+        <v>496205</v>
       </c>
       <c r="R5" t="n">
-        <v>7036020</v>
+        <v>7035804</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1133,17 +1137,13 @@
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1154,22 +1154,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1187,10 +1187,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131752891</v>
+        <v>131752962</v>
       </c>
       <c r="B6" t="n">
-        <v>91832</v>
+        <v>79264</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,30 +1198,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1229,10 +1225,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496242</v>
+        <v>496528</v>
       </c>
       <c r="R6" t="n">
-        <v>7035834</v>
+        <v>7036197</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1312,10 +1308,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131752962</v>
+        <v>131752891</v>
       </c>
       <c r="B7" t="n">
-        <v>79264</v>
+        <v>91832</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,26 +1319,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496528</v>
+        <v>496242</v>
       </c>
       <c r="R7" t="n">
-        <v>7036197</v>
+        <v>7035834</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1833,10 +1833,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131752924</v>
+        <v>131752963</v>
       </c>
       <c r="B11" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1844,31 +1844,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1876,10 +1871,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>496209</v>
+        <v>496243</v>
       </c>
       <c r="R11" t="n">
-        <v>7035774</v>
+        <v>7035811</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1916,7 +1911,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1925,6 +1920,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1943,14 +1939,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1968,7 +1959,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131752910</v>
+        <v>131752924</v>
       </c>
       <c r="B12" t="n">
         <v>57902</v>
@@ -2001,7 +1992,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2011,10 +2002,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>496471</v>
+        <v>496209</v>
       </c>
       <c r="R12" t="n">
-        <v>7036080</v>
+        <v>7035774</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2051,7 +2042,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2078,9 +2069,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2098,10 +2094,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131752963</v>
+        <v>131752910</v>
       </c>
       <c r="B13" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2109,26 +2105,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2136,10 +2137,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>496243</v>
+        <v>496471</v>
       </c>
       <c r="R13" t="n">
-        <v>7035811</v>
+        <v>7036080</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2176,7 +2177,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2185,7 +2186,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2484,10 +2484,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131752887</v>
+        <v>131752956</v>
       </c>
       <c r="B16" t="n">
-        <v>83244</v>
+        <v>91852</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2495,26 +2495,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2522,10 +2522,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>496531</v>
+        <v>496130</v>
       </c>
       <c r="R16" t="n">
-        <v>7036184</v>
+        <v>7035766</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2605,10 +2605,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131752905</v>
+        <v>131752943</v>
       </c>
       <c r="B17" t="n">
-        <v>57902</v>
+        <v>80369</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2616,31 +2616,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2648,10 +2643,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>496420</v>
+        <v>496214</v>
       </c>
       <c r="R17" t="n">
-        <v>7036158</v>
+        <v>7035803</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2686,17 +2681,13 @@
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2735,10 +2726,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131752903</v>
+        <v>131752887</v>
       </c>
       <c r="B18" t="n">
-        <v>57902</v>
+        <v>83244</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2746,31 +2737,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2778,10 +2764,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496454</v>
+        <v>496531</v>
       </c>
       <c r="R18" t="n">
-        <v>7036201</v>
+        <v>7036184</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2816,17 +2802,13 @@
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2865,10 +2847,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131752956</v>
+        <v>131752905</v>
       </c>
       <c r="B19" t="n">
-        <v>91852</v>
+        <v>57902</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2876,24 +2858,29 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2903,10 +2890,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>496130</v>
+        <v>496420</v>
       </c>
       <c r="R19" t="n">
-        <v>7035766</v>
+        <v>7036158</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2941,13 +2928,17 @@
           <t>2026-03-18</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2986,10 +2977,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131752943</v>
+        <v>131752903</v>
       </c>
       <c r="B20" t="n">
-        <v>80369</v>
+        <v>57902</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2997,26 +2988,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3024,10 +3020,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>496214</v>
+        <v>496454</v>
       </c>
       <c r="R20" t="n">
-        <v>7035803</v>
+        <v>7036201</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3062,13 +3058,17 @@
           <t>2026-03-18</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3362,10 +3362,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131752942</v>
+        <v>131752898</v>
       </c>
       <c r="B23" t="n">
-        <v>80370</v>
+        <v>57902</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3373,26 +3373,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3400,10 +3405,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496194</v>
+        <v>496293</v>
       </c>
       <c r="R23" t="n">
-        <v>7035755</v>
+        <v>7035984</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3438,13 +3443,17 @@
           <t>2026-03-18</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3455,17 +3464,22 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3483,7 +3497,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131752898</v>
+        <v>131752907</v>
       </c>
       <c r="B24" t="n">
         <v>57902</v>
@@ -3516,7 +3530,7 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3526,10 +3540,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>496293</v>
+        <v>496513</v>
       </c>
       <c r="R24" t="n">
-        <v>7035984</v>
+        <v>7036129</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3566,7 +3580,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3593,14 +3607,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3618,10 +3627,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131752907</v>
+        <v>131752942</v>
       </c>
       <c r="B25" t="n">
-        <v>57902</v>
+        <v>80370</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3629,31 +3638,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3661,10 +3665,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>496513</v>
+        <v>496194</v>
       </c>
       <c r="R25" t="n">
-        <v>7036129</v>
+        <v>7035755</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3699,17 +3703,13 @@
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3720,17 +3720,17 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3748,10 +3748,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131752919</v>
+        <v>131752961</v>
       </c>
       <c r="B26" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3759,31 +3759,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3791,10 +3786,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>496379</v>
+        <v>496271</v>
       </c>
       <c r="R26" t="n">
-        <v>7035973</v>
+        <v>7035921</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3831,7 +3826,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3840,6 +3835,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3858,14 +3854,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3883,10 +3874,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131752961</v>
+        <v>131752919</v>
       </c>
       <c r="B27" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3894,26 +3885,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3921,10 +3917,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>496271</v>
+        <v>496379</v>
       </c>
       <c r="R27" t="n">
-        <v>7035921</v>
+        <v>7035973</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3961,7 +3957,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3970,7 +3966,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3989,9 +3984,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -5311,10 +5311,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131752896</v>
+        <v>131752939</v>
       </c>
       <c r="B38" t="n">
-        <v>57902</v>
+        <v>80370</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5322,31 +5322,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -5354,10 +5349,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>496249</v>
+        <v>496130</v>
       </c>
       <c r="R38" t="n">
-        <v>7035881</v>
+        <v>7035728</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5392,17 +5387,13 @@
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en tall.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5413,17 +5404,22 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5441,10 +5437,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131752939</v>
+        <v>131752944</v>
       </c>
       <c r="B39" t="n">
-        <v>80370</v>
+        <v>80369</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5452,21 +5448,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5479,10 +5475,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>496130</v>
+        <v>496246</v>
       </c>
       <c r="R39" t="n">
-        <v>7035728</v>
+        <v>7035859</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5542,14 +5538,9 @@
           <t>Salix caprea</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5567,10 +5558,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131752944</v>
+        <v>131752896</v>
       </c>
       <c r="B40" t="n">
-        <v>80369</v>
+        <v>57902</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5578,26 +5569,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5605,10 +5601,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>496246</v>
+        <v>496249</v>
       </c>
       <c r="R40" t="n">
-        <v>7035859</v>
+        <v>7035881</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5643,13 +5639,17 @@
           <t>2026-03-18</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en tall.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5660,17 +5660,17 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5953,10 +5953,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131752958</v>
+        <v>131752941</v>
       </c>
       <c r="B43" t="n">
-        <v>91852</v>
+        <v>80370</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5964,26 +5964,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5991,10 +5991,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>496359</v>
+        <v>496195</v>
       </c>
       <c r="R43" t="n">
-        <v>7035980</v>
+        <v>7035791</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6046,17 +6046,22 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6074,10 +6079,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131752941</v>
+        <v>131752958</v>
       </c>
       <c r="B44" t="n">
-        <v>80370</v>
+        <v>91852</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6085,26 +6090,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -6112,10 +6117,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>496195</v>
+        <v>496359</v>
       </c>
       <c r="R44" t="n">
-        <v>7035791</v>
+        <v>7035980</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6167,22 +6172,17 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6200,10 +6200,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131752916</v>
+        <v>131752952</v>
       </c>
       <c r="B45" t="n">
-        <v>57902</v>
+        <v>80369</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6211,31 +6211,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6243,10 +6238,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>496424</v>
+        <v>496192</v>
       </c>
       <c r="R45" t="n">
-        <v>7036028</v>
+        <v>7035762</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6281,17 +6276,13 @@
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6302,17 +6293,22 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6330,10 +6326,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131752938</v>
+        <v>131752946</v>
       </c>
       <c r="B46" t="n">
-        <v>57902</v>
+        <v>80369</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6341,31 +6337,26 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6373,10 +6364,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>496294</v>
+        <v>496218</v>
       </c>
       <c r="R46" t="n">
-        <v>7035996</v>
+        <v>7035789</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6411,17 +6402,13 @@
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6432,22 +6419,17 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6465,7 +6447,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131752952</v>
+        <v>131752947</v>
       </c>
       <c r="B47" t="n">
         <v>80369</v>
@@ -6503,10 +6485,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>496192</v>
+        <v>496215</v>
       </c>
       <c r="R47" t="n">
-        <v>7035762</v>
+        <v>7035808</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6591,10 +6573,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131752947</v>
+        <v>131752916</v>
       </c>
       <c r="B48" t="n">
-        <v>80369</v>
+        <v>57902</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6602,26 +6584,31 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6629,10 +6616,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>496215</v>
+        <v>496424</v>
       </c>
       <c r="R48" t="n">
-        <v>7035808</v>
+        <v>7036028</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6667,13 +6654,17 @@
           <t>2026-03-18</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6684,22 +6675,17 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6717,10 +6703,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131752946</v>
+        <v>131752938</v>
       </c>
       <c r="B49" t="n">
-        <v>80369</v>
+        <v>57902</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6728,26 +6714,31 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6755,10 +6746,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>496218</v>
+        <v>496294</v>
       </c>
       <c r="R49" t="n">
-        <v>7035789</v>
+        <v>7035996</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6793,13 +6784,17 @@
           <t>2026-03-18</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6810,17 +6805,22 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6838,10 +6838,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131752940</v>
+        <v>131752945</v>
       </c>
       <c r="B50" t="n">
-        <v>80370</v>
+        <v>80369</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6849,21 +6849,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6876,10 +6876,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>496212</v>
+        <v>496358</v>
       </c>
       <c r="R50" t="n">
-        <v>7035799</v>
+        <v>7035946</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6959,10 +6959,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131752945</v>
+        <v>131752940</v>
       </c>
       <c r="B51" t="n">
-        <v>80369</v>
+        <v>80370</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6970,21 +6970,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6997,10 +6997,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>496358</v>
+        <v>496212</v>
       </c>
       <c r="R51" t="n">
-        <v>7035946</v>
+        <v>7035799</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>

--- a/artfynd/A 6929-2026 artfynd.xlsx
+++ b/artfynd/A 6929-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131752909</v>
+        <v>131752957</v>
       </c>
       <c r="B2" t="n">
-        <v>57902</v>
+        <v>91852</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,29 +686,24 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>496478</v>
+        <v>496342</v>
       </c>
       <c r="R2" t="n">
-        <v>7036088</v>
+        <v>7036007</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,17 +751,13 @@
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -805,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131752901</v>
+        <v>131752950</v>
       </c>
       <c r="B3" t="n">
-        <v>57902</v>
+        <v>80369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,31 +807,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -848,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496305</v>
+        <v>496205</v>
       </c>
       <c r="R3" t="n">
-        <v>7036020</v>
+        <v>7035804</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,17 +872,13 @@
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -907,22 +889,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -940,10 +922,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131752957</v>
+        <v>131752901</v>
       </c>
       <c r="B4" t="n">
-        <v>91852</v>
+        <v>57902</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -951,24 +933,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -978,10 +965,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496342</v>
+        <v>496305</v>
       </c>
       <c r="R4" t="n">
-        <v>7036007</v>
+        <v>7036020</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1016,13 +1003,17 @@
           <t>2026-03-18</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1041,9 +1032,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1061,10 +1057,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131752950</v>
+        <v>131752909</v>
       </c>
       <c r="B5" t="n">
-        <v>80369</v>
+        <v>57902</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1072,26 +1068,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1099,10 +1100,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>496205</v>
+        <v>496478</v>
       </c>
       <c r="R5" t="n">
-        <v>7035804</v>
+        <v>7036088</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1137,13 +1138,17 @@
           <t>2026-03-18</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1154,22 +1159,17 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1187,10 +1187,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131752962</v>
+        <v>131752891</v>
       </c>
       <c r="B6" t="n">
-        <v>79264</v>
+        <v>91832</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,26 +1198,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1225,10 +1229,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496528</v>
+        <v>496242</v>
       </c>
       <c r="R6" t="n">
-        <v>7036197</v>
+        <v>7035834</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1308,10 +1312,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131752891</v>
+        <v>131752962</v>
       </c>
       <c r="B7" t="n">
-        <v>91832</v>
+        <v>79264</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,30 +1323,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496242</v>
+        <v>496528</v>
       </c>
       <c r="R7" t="n">
-        <v>7035834</v>
+        <v>7036197</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -3362,10 +3362,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131752898</v>
+        <v>131752942</v>
       </c>
       <c r="B23" t="n">
-        <v>57902</v>
+        <v>80370</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3373,31 +3373,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3405,10 +3400,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496293</v>
+        <v>496194</v>
       </c>
       <c r="R23" t="n">
-        <v>7035984</v>
+        <v>7035755</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3443,17 +3438,13 @@
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3464,22 +3455,17 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3497,7 +3483,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131752907</v>
+        <v>131752898</v>
       </c>
       <c r="B24" t="n">
         <v>57902</v>
@@ -3530,7 +3516,7 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3540,10 +3526,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>496513</v>
+        <v>496293</v>
       </c>
       <c r="R24" t="n">
-        <v>7036129</v>
+        <v>7035984</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3580,7 +3566,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3607,9 +3593,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3627,10 +3618,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131752942</v>
+        <v>131752907</v>
       </c>
       <c r="B25" t="n">
-        <v>80370</v>
+        <v>57902</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3638,26 +3629,31 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3665,10 +3661,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>496194</v>
+        <v>496513</v>
       </c>
       <c r="R25" t="n">
-        <v>7035755</v>
+        <v>7036129</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3703,13 +3699,17 @@
           <t>2026-03-18</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3720,17 +3720,17 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4009,39 +4009,40 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131752890</v>
+        <v>131752917</v>
       </c>
       <c r="B28" t="n">
-        <v>91795</v>
+        <v>57902</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -4051,10 +4052,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>496286</v>
+        <v>496409</v>
       </c>
       <c r="R28" t="n">
-        <v>7035879</v>
+        <v>7036004</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4089,13 +4090,17 @@
           <t>2026-03-18</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4114,9 +4119,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4134,7 +4144,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131752917</v>
+        <v>131752906</v>
       </c>
       <c r="B29" t="n">
         <v>57902</v>
@@ -4167,7 +4177,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4177,10 +4187,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>496409</v>
+        <v>496475</v>
       </c>
       <c r="R29" t="n">
-        <v>7036004</v>
+        <v>7036177</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4217,7 +4227,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4244,14 +4254,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4269,7 +4274,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131752906</v>
+        <v>131752908</v>
       </c>
       <c r="B30" t="n">
         <v>57902</v>
@@ -4312,10 +4317,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>496475</v>
+        <v>496506</v>
       </c>
       <c r="R30" t="n">
-        <v>7036177</v>
+        <v>7036124</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4399,7 +4404,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131752908</v>
+        <v>131752897</v>
       </c>
       <c r="B31" t="n">
         <v>57902</v>
@@ -4432,7 +4437,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4442,10 +4447,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>496506</v>
+        <v>496304</v>
       </c>
       <c r="R31" t="n">
-        <v>7036124</v>
+        <v>7035979</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4482,7 +4487,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4509,9 +4514,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4529,7 +4539,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131752897</v>
+        <v>131752900</v>
       </c>
       <c r="B32" t="n">
         <v>57902</v>
@@ -4572,10 +4582,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>496304</v>
+        <v>496293</v>
       </c>
       <c r="R32" t="n">
-        <v>7035979</v>
+        <v>7035993</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4664,40 +4674,39 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131752900</v>
+        <v>131752890</v>
       </c>
       <c r="B33" t="n">
-        <v>57902</v>
+        <v>91795</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4707,10 +4716,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>496293</v>
+        <v>496286</v>
       </c>
       <c r="R33" t="n">
-        <v>7035993</v>
+        <v>7035879</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4745,17 +4754,13 @@
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4774,14 +4779,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5064,10 +5064,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131752949</v>
+        <v>131752953</v>
       </c>
       <c r="B36" t="n">
-        <v>80369</v>
+        <v>78276</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5075,21 +5075,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -5102,10 +5102,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>496198</v>
+        <v>496536</v>
       </c>
       <c r="R36" t="n">
-        <v>7035790</v>
+        <v>7036191</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5157,22 +5157,17 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5190,10 +5185,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131752953</v>
+        <v>131752949</v>
       </c>
       <c r="B37" t="n">
-        <v>78276</v>
+        <v>80369</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5201,21 +5196,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5228,10 +5223,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>496536</v>
+        <v>496198</v>
       </c>
       <c r="R37" t="n">
-        <v>7036191</v>
+        <v>7035790</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5283,17 +5278,22 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5311,10 +5311,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131752939</v>
+        <v>131752944</v>
       </c>
       <c r="B38" t="n">
-        <v>80370</v>
+        <v>80369</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5322,21 +5322,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5349,10 +5349,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>496130</v>
+        <v>496246</v>
       </c>
       <c r="R38" t="n">
-        <v>7035728</v>
+        <v>7035859</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5412,14 +5412,9 @@
           <t>Salix caprea</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5437,10 +5432,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131752944</v>
+        <v>131752896</v>
       </c>
       <c r="B39" t="n">
-        <v>80369</v>
+        <v>57902</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5448,26 +5443,31 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5475,10 +5475,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>496246</v>
+        <v>496249</v>
       </c>
       <c r="R39" t="n">
-        <v>7035859</v>
+        <v>7035881</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5513,13 +5513,17 @@
           <t>2026-03-18</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en tall.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5530,17 +5534,17 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5558,10 +5562,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131752896</v>
+        <v>131752939</v>
       </c>
       <c r="B40" t="n">
-        <v>57902</v>
+        <v>80370</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5569,31 +5573,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5601,10 +5600,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>496249</v>
+        <v>496130</v>
       </c>
       <c r="R40" t="n">
-        <v>7035881</v>
+        <v>7035728</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5639,17 +5638,13 @@
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en tall.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5660,17 +5655,22 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5953,10 +5953,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131752941</v>
+        <v>131752958</v>
       </c>
       <c r="B43" t="n">
-        <v>80370</v>
+        <v>91852</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5964,26 +5964,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5991,10 +5991,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>496195</v>
+        <v>496359</v>
       </c>
       <c r="R43" t="n">
-        <v>7035791</v>
+        <v>7035980</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6046,22 +6046,17 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6079,10 +6074,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131752958</v>
+        <v>131752941</v>
       </c>
       <c r="B44" t="n">
-        <v>91852</v>
+        <v>80370</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6090,26 +6085,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -6117,10 +6112,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>496359</v>
+        <v>496195</v>
       </c>
       <c r="R44" t="n">
-        <v>7035980</v>
+        <v>7035791</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6172,17 +6167,22 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6838,10 +6838,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131752945</v>
+        <v>131752940</v>
       </c>
       <c r="B50" t="n">
-        <v>80369</v>
+        <v>80370</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6849,21 +6849,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6876,10 +6876,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>496358</v>
+        <v>496212</v>
       </c>
       <c r="R50" t="n">
-        <v>7035946</v>
+        <v>7035799</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6959,10 +6959,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131752940</v>
+        <v>131752945</v>
       </c>
       <c r="B51" t="n">
-        <v>80370</v>
+        <v>80369</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6970,21 +6970,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6997,10 +6997,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>496212</v>
+        <v>496358</v>
       </c>
       <c r="R51" t="n">
-        <v>7035799</v>
+        <v>7035946</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>

--- a/artfynd/A 6929-2026 artfynd.xlsx
+++ b/artfynd/A 6929-2026 artfynd.xlsx
@@ -2847,7 +2847,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131752905</v>
+        <v>131752903</v>
       </c>
       <c r="B19" t="n">
         <v>57902</v>
@@ -2890,10 +2890,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>496420</v>
+        <v>496454</v>
       </c>
       <c r="R19" t="n">
-        <v>7036158</v>
+        <v>7036201</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2977,7 +2977,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131752903</v>
+        <v>131752905</v>
       </c>
       <c r="B20" t="n">
         <v>57902</v>
@@ -3020,10 +3020,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>496454</v>
+        <v>496420</v>
       </c>
       <c r="R20" t="n">
-        <v>7036201</v>
+        <v>7036158</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -5311,10 +5311,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131752944</v>
+        <v>131752939</v>
       </c>
       <c r="B38" t="n">
-        <v>80369</v>
+        <v>80370</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5322,21 +5322,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5349,10 +5349,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>496246</v>
+        <v>496130</v>
       </c>
       <c r="R38" t="n">
-        <v>7035859</v>
+        <v>7035728</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5412,9 +5412,14 @@
           <t>Salix caprea</t>
         </is>
       </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5562,10 +5567,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131752939</v>
+        <v>131752944</v>
       </c>
       <c r="B40" t="n">
-        <v>80370</v>
+        <v>80369</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5573,21 +5578,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5600,10 +5605,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>496130</v>
+        <v>496246</v>
       </c>
       <c r="R40" t="n">
-        <v>7035728</v>
+        <v>7035859</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5663,14 +5668,9 @@
           <t>Salix caprea</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5953,10 +5953,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131752958</v>
+        <v>131752941</v>
       </c>
       <c r="B43" t="n">
-        <v>91852</v>
+        <v>80370</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5964,26 +5964,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5991,10 +5991,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>496359</v>
+        <v>496195</v>
       </c>
       <c r="R43" t="n">
-        <v>7035980</v>
+        <v>7035791</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6046,17 +6046,22 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6074,10 +6079,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131752941</v>
+        <v>131752958</v>
       </c>
       <c r="B44" t="n">
-        <v>80370</v>
+        <v>91852</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6085,26 +6090,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -6112,10 +6117,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>496195</v>
+        <v>496359</v>
       </c>
       <c r="R44" t="n">
-        <v>7035791</v>
+        <v>7035980</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6167,22 +6172,17 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6200,10 +6200,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131752952</v>
+        <v>131752916</v>
       </c>
       <c r="B45" t="n">
-        <v>80369</v>
+        <v>57902</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6211,26 +6211,31 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6238,10 +6243,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>496192</v>
+        <v>496424</v>
       </c>
       <c r="R45" t="n">
-        <v>7035762</v>
+        <v>7036028</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6276,13 +6281,17 @@
           <t>2026-03-18</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6293,22 +6302,17 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6326,10 +6330,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131752946</v>
+        <v>131752938</v>
       </c>
       <c r="B46" t="n">
-        <v>80369</v>
+        <v>57902</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6337,26 +6341,31 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6364,10 +6373,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>496218</v>
+        <v>496294</v>
       </c>
       <c r="R46" t="n">
-        <v>7035789</v>
+        <v>7035996</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6402,13 +6411,17 @@
           <t>2026-03-18</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6419,17 +6432,22 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6447,7 +6465,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131752947</v>
+        <v>131752952</v>
       </c>
       <c r="B47" t="n">
         <v>80369</v>
@@ -6485,10 +6503,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>496215</v>
+        <v>496192</v>
       </c>
       <c r="R47" t="n">
-        <v>7035808</v>
+        <v>7035762</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6573,10 +6591,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131752916</v>
+        <v>131752946</v>
       </c>
       <c r="B48" t="n">
-        <v>57902</v>
+        <v>80369</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6584,31 +6602,26 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6616,10 +6629,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>496424</v>
+        <v>496218</v>
       </c>
       <c r="R48" t="n">
-        <v>7036028</v>
+        <v>7035789</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6654,17 +6667,13 @@
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6675,17 +6684,17 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6703,10 +6712,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131752938</v>
+        <v>131752947</v>
       </c>
       <c r="B49" t="n">
-        <v>57902</v>
+        <v>80369</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6714,31 +6723,26 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6746,10 +6750,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>496294</v>
+        <v>496215</v>
       </c>
       <c r="R49" t="n">
-        <v>7035996</v>
+        <v>7035808</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6784,17 +6788,13 @@
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6805,22 +6805,22 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>

--- a/artfynd/A 6929-2026 artfynd.xlsx
+++ b/artfynd/A 6929-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131752957</v>
       </c>
       <c r="B2" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>131752950</v>
       </c>
       <c r="B3" t="n">
-        <v>80369</v>
+        <v>80371</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,10 +922,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131752901</v>
+        <v>131752909</v>
       </c>
       <c r="B4" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -965,10 +965,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496305</v>
+        <v>496478</v>
       </c>
       <c r="R4" t="n">
-        <v>7036020</v>
+        <v>7036088</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,14 +1032,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1057,10 +1052,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131752909</v>
+        <v>131752901</v>
       </c>
       <c r="B5" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1085,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1100,10 +1095,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>496478</v>
+        <v>496305</v>
       </c>
       <c r="R5" t="n">
-        <v>7036088</v>
+        <v>7036020</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1140,7 +1135,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1167,9 +1162,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1190,7 +1190,7 @@
         <v>131752891</v>
       </c>
       <c r="B6" t="n">
-        <v>91832</v>
+        <v>91838</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>131752962</v>
       </c>
       <c r="B7" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>131752918</v>
       </c>
       <c r="B8" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>131752915</v>
       </c>
       <c r="B9" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>131752914</v>
       </c>
       <c r="B10" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>131752963</v>
       </c>
       <c r="B11" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>131752924</v>
       </c>
       <c r="B12" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>131752910</v>
       </c>
       <c r="B13" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>131752913</v>
       </c>
       <c r="B14" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>131752923</v>
       </c>
       <c r="B15" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>131752956</v>
       </c>
       <c r="B16" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2605,10 +2605,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131752943</v>
+        <v>131752887</v>
       </c>
       <c r="B17" t="n">
-        <v>80369</v>
+        <v>83246</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2616,21 +2616,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>496214</v>
+        <v>496531</v>
       </c>
       <c r="R17" t="n">
-        <v>7035803</v>
+        <v>7036184</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2726,10 +2726,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131752887</v>
+        <v>131752943</v>
       </c>
       <c r="B18" t="n">
-        <v>83244</v>
+        <v>80371</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2737,21 +2737,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496531</v>
+        <v>496214</v>
       </c>
       <c r="R18" t="n">
-        <v>7036184</v>
+        <v>7035803</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2847,10 +2847,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131752903</v>
+        <v>131752905</v>
       </c>
       <c r="B19" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2890,10 +2890,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>496454</v>
+        <v>496420</v>
       </c>
       <c r="R19" t="n">
-        <v>7036201</v>
+        <v>7036158</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2977,10 +2977,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131752905</v>
+        <v>131752903</v>
       </c>
       <c r="B20" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3020,10 +3020,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>496420</v>
+        <v>496454</v>
       </c>
       <c r="R20" t="n">
-        <v>7036158</v>
+        <v>7036201</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3107,10 +3107,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131752955</v>
+        <v>131752920</v>
       </c>
       <c r="B21" t="n">
-        <v>91828</v>
+        <v>57904</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3118,28 +3118,29 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3149,10 +3150,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>496475</v>
+        <v>496360</v>
       </c>
       <c r="R21" t="n">
-        <v>7036170</v>
+        <v>7035948</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3187,13 +3188,17 @@
           <t>2026-03-18</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3232,10 +3237,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131752920</v>
+        <v>131752955</v>
       </c>
       <c r="B22" t="n">
-        <v>57902</v>
+        <v>91834</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3243,29 +3248,28 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3275,10 +3279,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496360</v>
+        <v>496475</v>
       </c>
       <c r="R22" t="n">
-        <v>7035948</v>
+        <v>7036170</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3313,17 +3317,13 @@
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3362,10 +3362,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131752942</v>
+        <v>131752898</v>
       </c>
       <c r="B23" t="n">
-        <v>80370</v>
+        <v>57904</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3373,26 +3373,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3400,10 +3405,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496194</v>
+        <v>496293</v>
       </c>
       <c r="R23" t="n">
-        <v>7035755</v>
+        <v>7035984</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3438,13 +3443,17 @@
           <t>2026-03-18</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3455,17 +3464,22 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3483,10 +3497,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131752898</v>
+        <v>131752907</v>
       </c>
       <c r="B24" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3516,7 +3530,7 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3526,10 +3540,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>496293</v>
+        <v>496513</v>
       </c>
       <c r="R24" t="n">
-        <v>7035984</v>
+        <v>7036129</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3566,7 +3580,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3593,14 +3607,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3618,10 +3627,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131752907</v>
+        <v>131752942</v>
       </c>
       <c r="B25" t="n">
-        <v>57902</v>
+        <v>80372</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3629,31 +3638,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3661,10 +3665,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>496513</v>
+        <v>496194</v>
       </c>
       <c r="R25" t="n">
-        <v>7036129</v>
+        <v>7035755</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3699,17 +3703,13 @@
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3720,17 +3720,17 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3751,7 +3751,7 @@
         <v>131752961</v>
       </c>
       <c r="B26" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>131752919</v>
       </c>
       <c r="B27" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4009,40 +4009,39 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131752917</v>
+        <v>131752890</v>
       </c>
       <c r="B28" t="n">
-        <v>57902</v>
+        <v>91801</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -4052,10 +4051,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>496409</v>
+        <v>496286</v>
       </c>
       <c r="R28" t="n">
-        <v>7036004</v>
+        <v>7035879</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4090,17 +4089,13 @@
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4119,14 +4114,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4144,10 +4134,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131752906</v>
+        <v>131752917</v>
       </c>
       <c r="B29" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4177,7 +4167,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4187,10 +4177,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>496475</v>
+        <v>496409</v>
       </c>
       <c r="R29" t="n">
-        <v>7036177</v>
+        <v>7036004</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4227,7 +4217,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4254,9 +4244,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4274,10 +4269,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131752908</v>
+        <v>131752906</v>
       </c>
       <c r="B30" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4317,10 +4312,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>496506</v>
+        <v>496475</v>
       </c>
       <c r="R30" t="n">
-        <v>7036124</v>
+        <v>7036177</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4404,10 +4399,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131752897</v>
+        <v>131752908</v>
       </c>
       <c r="B31" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4437,7 +4432,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4447,10 +4442,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>496304</v>
+        <v>496506</v>
       </c>
       <c r="R31" t="n">
-        <v>7035979</v>
+        <v>7036124</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4487,7 +4482,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4514,14 +4509,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4539,10 +4529,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131752900</v>
+        <v>131752897</v>
       </c>
       <c r="B32" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4582,10 +4572,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>496293</v>
+        <v>496304</v>
       </c>
       <c r="R32" t="n">
-        <v>7035993</v>
+        <v>7035979</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4674,39 +4664,40 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131752890</v>
+        <v>131752900</v>
       </c>
       <c r="B33" t="n">
-        <v>91795</v>
+        <v>57904</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4716,10 +4707,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>496286</v>
+        <v>496293</v>
       </c>
       <c r="R33" t="n">
-        <v>7035879</v>
+        <v>7035993</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4754,13 +4745,17 @@
           <t>2026-03-18</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4779,9 +4774,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4802,7 +4802,7 @@
         <v>131752922</v>
       </c>
       <c r="B34" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>131752911</v>
       </c>
       <c r="B35" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>131752953</v>
       </c>
       <c r="B36" t="n">
-        <v>78276</v>
+        <v>78278</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         <v>131752949</v>
       </c>
       <c r="B37" t="n">
-        <v>80369</v>
+        <v>80371</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5311,10 +5311,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131752939</v>
+        <v>131752944</v>
       </c>
       <c r="B38" t="n">
-        <v>80370</v>
+        <v>80371</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5322,21 +5322,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5349,10 +5349,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>496130</v>
+        <v>496246</v>
       </c>
       <c r="R38" t="n">
-        <v>7035728</v>
+        <v>7035859</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5412,14 +5412,9 @@
           <t>Salix caprea</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5437,10 +5432,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131752896</v>
+        <v>131752939</v>
       </c>
       <c r="B39" t="n">
-        <v>57902</v>
+        <v>80372</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5448,31 +5443,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5480,10 +5470,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>496249</v>
+        <v>496130</v>
       </c>
       <c r="R39" t="n">
-        <v>7035881</v>
+        <v>7035728</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5518,17 +5508,13 @@
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en tall.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5539,17 +5525,22 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5567,10 +5558,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131752944</v>
+        <v>131752896</v>
       </c>
       <c r="B40" t="n">
-        <v>80369</v>
+        <v>57904</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5578,26 +5569,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5605,10 +5601,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>496246</v>
+        <v>496249</v>
       </c>
       <c r="R40" t="n">
-        <v>7035859</v>
+        <v>7035881</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5643,13 +5639,17 @@
           <t>2026-03-18</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en tall.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5660,17 +5660,17 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5691,7 +5691,7 @@
         <v>131752912</v>
       </c>
       <c r="B41" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5821,7 +5821,7 @@
         <v>131752902</v>
       </c>
       <c r="B42" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5953,10 +5953,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131752941</v>
+        <v>131752958</v>
       </c>
       <c r="B43" t="n">
-        <v>80370</v>
+        <v>91858</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5964,26 +5964,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5991,10 +5991,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>496195</v>
+        <v>496359</v>
       </c>
       <c r="R43" t="n">
-        <v>7035791</v>
+        <v>7035980</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6046,22 +6046,17 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6079,10 +6074,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131752958</v>
+        <v>131752941</v>
       </c>
       <c r="B44" t="n">
-        <v>91852</v>
+        <v>80372</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6090,26 +6085,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -6117,10 +6112,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>496359</v>
+        <v>496195</v>
       </c>
       <c r="R44" t="n">
-        <v>7035980</v>
+        <v>7035791</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6172,17 +6167,22 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6200,10 +6200,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131752916</v>
+        <v>131752947</v>
       </c>
       <c r="B45" t="n">
-        <v>57902</v>
+        <v>80371</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6211,31 +6211,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6243,10 +6238,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>496424</v>
+        <v>496215</v>
       </c>
       <c r="R45" t="n">
-        <v>7036028</v>
+        <v>7035808</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6281,17 +6276,13 @@
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6302,17 +6293,22 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6330,10 +6326,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131752938</v>
+        <v>131752946</v>
       </c>
       <c r="B46" t="n">
-        <v>57902</v>
+        <v>80371</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6341,31 +6337,26 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6373,10 +6364,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>496294</v>
+        <v>496218</v>
       </c>
       <c r="R46" t="n">
-        <v>7035996</v>
+        <v>7035789</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6411,17 +6402,13 @@
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6432,22 +6419,17 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6468,7 +6450,7 @@
         <v>131752952</v>
       </c>
       <c r="B47" t="n">
-        <v>80369</v>
+        <v>80371</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6591,10 +6573,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131752946</v>
+        <v>131752916</v>
       </c>
       <c r="B48" t="n">
-        <v>80369</v>
+        <v>57904</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6602,26 +6584,31 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6629,10 +6616,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>496218</v>
+        <v>496424</v>
       </c>
       <c r="R48" t="n">
-        <v>7035789</v>
+        <v>7036028</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6667,13 +6654,17 @@
           <t>2026-03-18</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6684,17 +6675,17 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6712,10 +6703,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131752947</v>
+        <v>131752938</v>
       </c>
       <c r="B49" t="n">
-        <v>80369</v>
+        <v>57904</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6723,26 +6714,31 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6750,10 +6746,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>496215</v>
+        <v>496294</v>
       </c>
       <c r="R49" t="n">
-        <v>7035808</v>
+        <v>7035996</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6788,13 +6784,17 @@
           <t>2026-03-18</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6805,22 +6805,22 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6838,10 +6838,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131752940</v>
+        <v>131752945</v>
       </c>
       <c r="B50" t="n">
-        <v>80370</v>
+        <v>80371</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6849,21 +6849,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6876,10 +6876,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>496212</v>
+        <v>496358</v>
       </c>
       <c r="R50" t="n">
-        <v>7035799</v>
+        <v>7035946</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6959,10 +6959,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131752945</v>
+        <v>131752940</v>
       </c>
       <c r="B51" t="n">
-        <v>80369</v>
+        <v>80372</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6970,21 +6970,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6997,10 +6997,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>496358</v>
+        <v>496212</v>
       </c>
       <c r="R51" t="n">
-        <v>7035946</v>
+        <v>7035799</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7083,7 +7083,7 @@
         <v>131752951</v>
       </c>
       <c r="B52" t="n">
-        <v>80369</v>
+        <v>80371</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>131752904</v>
       </c>
       <c r="B53" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 6929-2026 artfynd.xlsx
+++ b/artfynd/A 6929-2026 artfynd.xlsx
@@ -1187,10 +1187,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131752891</v>
+        <v>131752962</v>
       </c>
       <c r="B6" t="n">
-        <v>91838</v>
+        <v>79266</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,30 +1198,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1229,10 +1225,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496242</v>
+        <v>496528</v>
       </c>
       <c r="R6" t="n">
-        <v>7035834</v>
+        <v>7036197</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1312,10 +1308,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131752962</v>
+        <v>131752891</v>
       </c>
       <c r="B7" t="n">
-        <v>79266</v>
+        <v>91838</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,26 +1319,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496528</v>
+        <v>496242</v>
       </c>
       <c r="R7" t="n">
-        <v>7036197</v>
+        <v>7035834</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -5064,10 +5064,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131752953</v>
+        <v>131752949</v>
       </c>
       <c r="B36" t="n">
-        <v>78278</v>
+        <v>80371</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5075,21 +5075,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -5102,10 +5102,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>496536</v>
+        <v>496198</v>
       </c>
       <c r="R36" t="n">
-        <v>7036191</v>
+        <v>7035790</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5157,17 +5157,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5185,10 +5190,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131752949</v>
+        <v>131752953</v>
       </c>
       <c r="B37" t="n">
-        <v>80371</v>
+        <v>78278</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5196,21 +5201,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5223,10 +5228,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>496198</v>
+        <v>496536</v>
       </c>
       <c r="R37" t="n">
-        <v>7035790</v>
+        <v>7036191</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5278,22 +5283,17 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -6200,7 +6200,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131752947</v>
+        <v>131752952</v>
       </c>
       <c r="B45" t="n">
         <v>80371</v>
@@ -6238,10 +6238,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>496215</v>
+        <v>496192</v>
       </c>
       <c r="R45" t="n">
-        <v>7035808</v>
+        <v>7035762</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6326,7 +6326,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131752946</v>
+        <v>131752947</v>
       </c>
       <c r="B46" t="n">
         <v>80371</v>
@@ -6364,10 +6364,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>496218</v>
+        <v>496215</v>
       </c>
       <c r="R46" t="n">
-        <v>7035789</v>
+        <v>7035808</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6419,17 +6419,22 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6447,7 +6452,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131752952</v>
+        <v>131752946</v>
       </c>
       <c r="B47" t="n">
         <v>80371</v>
@@ -6485,10 +6490,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>496192</v>
+        <v>496218</v>
       </c>
       <c r="R47" t="n">
-        <v>7035762</v>
+        <v>7035789</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6540,22 +6545,17 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>

--- a/artfynd/A 6929-2026 artfynd.xlsx
+++ b/artfynd/A 6929-2026 artfynd.xlsx
@@ -1187,10 +1187,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131752962</v>
+        <v>131752891</v>
       </c>
       <c r="B6" t="n">
-        <v>79266</v>
+        <v>91838</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,26 +1198,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1225,10 +1229,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496528</v>
+        <v>496242</v>
       </c>
       <c r="R6" t="n">
-        <v>7036197</v>
+        <v>7035834</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1308,10 +1312,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131752891</v>
+        <v>131752962</v>
       </c>
       <c r="B7" t="n">
-        <v>91838</v>
+        <v>79266</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,30 +1323,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496242</v>
+        <v>496528</v>
       </c>
       <c r="R7" t="n">
-        <v>7035834</v>
+        <v>7036197</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -5953,10 +5953,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131752958</v>
+        <v>131752941</v>
       </c>
       <c r="B43" t="n">
-        <v>91858</v>
+        <v>80372</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5964,26 +5964,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5991,10 +5991,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>496359</v>
+        <v>496195</v>
       </c>
       <c r="R43" t="n">
-        <v>7035980</v>
+        <v>7035791</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6046,17 +6046,22 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6074,10 +6079,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131752941</v>
+        <v>131752958</v>
       </c>
       <c r="B44" t="n">
-        <v>80372</v>
+        <v>91858</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6085,26 +6090,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -6112,10 +6117,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>496195</v>
+        <v>496359</v>
       </c>
       <c r="R44" t="n">
-        <v>7035791</v>
+        <v>7035980</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6167,22 +6172,17 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>

--- a/artfynd/A 6929-2026 artfynd.xlsx
+++ b/artfynd/A 6929-2026 artfynd.xlsx
@@ -2605,10 +2605,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131752887</v>
+        <v>131752905</v>
       </c>
       <c r="B17" t="n">
-        <v>83246</v>
+        <v>57904</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2616,26 +2616,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2643,10 +2648,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>496531</v>
+        <v>496420</v>
       </c>
       <c r="R17" t="n">
-        <v>7036184</v>
+        <v>7036158</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2681,13 +2686,17 @@
           <t>2026-03-18</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2726,10 +2735,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131752943</v>
+        <v>131752903</v>
       </c>
       <c r="B18" t="n">
-        <v>80371</v>
+        <v>57904</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2737,26 +2746,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2764,10 +2778,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496214</v>
+        <v>496454</v>
       </c>
       <c r="R18" t="n">
-        <v>7035803</v>
+        <v>7036201</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2802,13 +2816,17 @@
           <t>2026-03-18</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2847,10 +2865,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131752905</v>
+        <v>131752943</v>
       </c>
       <c r="B19" t="n">
-        <v>57904</v>
+        <v>80371</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2858,31 +2876,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2890,10 +2903,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>496420</v>
+        <v>496214</v>
       </c>
       <c r="R19" t="n">
-        <v>7036158</v>
+        <v>7035803</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2928,17 +2941,13 @@
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2977,10 +2986,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131752903</v>
+        <v>131752887</v>
       </c>
       <c r="B20" t="n">
-        <v>57904</v>
+        <v>83246</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2988,31 +2997,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3020,10 +3024,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>496454</v>
+        <v>496531</v>
       </c>
       <c r="R20" t="n">
-        <v>7036201</v>
+        <v>7036184</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3058,17 +3062,13 @@
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -4009,39 +4009,40 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131752890</v>
+        <v>131752917</v>
       </c>
       <c r="B28" t="n">
-        <v>91801</v>
+        <v>57904</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -4051,10 +4052,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>496286</v>
+        <v>496409</v>
       </c>
       <c r="R28" t="n">
-        <v>7035879</v>
+        <v>7036004</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4089,13 +4090,17 @@
           <t>2026-03-18</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4114,9 +4119,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4134,7 +4144,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131752917</v>
+        <v>131752906</v>
       </c>
       <c r="B29" t="n">
         <v>57904</v>
@@ -4167,7 +4177,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4177,10 +4187,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>496409</v>
+        <v>496475</v>
       </c>
       <c r="R29" t="n">
-        <v>7036004</v>
+        <v>7036177</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4217,7 +4227,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4244,14 +4254,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4269,7 +4274,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131752906</v>
+        <v>131752908</v>
       </c>
       <c r="B30" t="n">
         <v>57904</v>
@@ -4312,10 +4317,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>496475</v>
+        <v>496506</v>
       </c>
       <c r="R30" t="n">
-        <v>7036177</v>
+        <v>7036124</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4399,7 +4404,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131752908</v>
+        <v>131752897</v>
       </c>
       <c r="B31" t="n">
         <v>57904</v>
@@ -4432,7 +4437,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4442,10 +4447,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>496506</v>
+        <v>496304</v>
       </c>
       <c r="R31" t="n">
-        <v>7036124</v>
+        <v>7035979</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4482,7 +4487,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4509,9 +4514,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4529,7 +4539,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131752897</v>
+        <v>131752900</v>
       </c>
       <c r="B32" t="n">
         <v>57904</v>
@@ -4572,10 +4582,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>496304</v>
+        <v>496293</v>
       </c>
       <c r="R32" t="n">
-        <v>7035979</v>
+        <v>7035993</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4664,40 +4674,39 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131752900</v>
+        <v>131752890</v>
       </c>
       <c r="B33" t="n">
-        <v>57904</v>
+        <v>91801</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4707,10 +4716,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>496293</v>
+        <v>496286</v>
       </c>
       <c r="R33" t="n">
-        <v>7035993</v>
+        <v>7035879</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4745,17 +4754,13 @@
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4774,14 +4779,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5064,10 +5064,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131752949</v>
+        <v>131752953</v>
       </c>
       <c r="B36" t="n">
-        <v>80371</v>
+        <v>78278</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5075,21 +5075,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -5102,10 +5102,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>496198</v>
+        <v>496536</v>
       </c>
       <c r="R36" t="n">
-        <v>7035790</v>
+        <v>7036191</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5157,22 +5157,17 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5190,10 +5185,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131752953</v>
+        <v>131752949</v>
       </c>
       <c r="B37" t="n">
-        <v>78278</v>
+        <v>80371</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5201,21 +5196,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5228,10 +5223,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>496536</v>
+        <v>496198</v>
       </c>
       <c r="R37" t="n">
-        <v>7036191</v>
+        <v>7035790</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5283,17 +5278,22 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>

--- a/artfynd/A 6929-2026 artfynd.xlsx
+++ b/artfynd/A 6929-2026 artfynd.xlsx
@@ -1187,10 +1187,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131752891</v>
+        <v>131752962</v>
       </c>
       <c r="B6" t="n">
-        <v>91838</v>
+        <v>79266</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,30 +1198,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1229,10 +1225,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496242</v>
+        <v>496528</v>
       </c>
       <c r="R6" t="n">
-        <v>7035834</v>
+        <v>7036197</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1312,10 +1308,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131752962</v>
+        <v>131752891</v>
       </c>
       <c r="B7" t="n">
-        <v>79266</v>
+        <v>91838</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,26 +1319,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496528</v>
+        <v>496242</v>
       </c>
       <c r="R7" t="n">
-        <v>7036197</v>
+        <v>7035834</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 6929-2026 artfynd.xlsx
+++ b/artfynd/A 6929-2026 artfynd.xlsx
@@ -1187,10 +1187,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131752962</v>
+        <v>131752891</v>
       </c>
       <c r="B6" t="n">
-        <v>79266</v>
+        <v>91838</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,26 +1198,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1225,10 +1229,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496528</v>
+        <v>496242</v>
       </c>
       <c r="R6" t="n">
-        <v>7036197</v>
+        <v>7035834</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1308,10 +1312,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131752891</v>
+        <v>131752962</v>
       </c>
       <c r="B7" t="n">
-        <v>91838</v>
+        <v>79266</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,30 +1323,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496242</v>
+        <v>496528</v>
       </c>
       <c r="R7" t="n">
-        <v>7035834</v>
+        <v>7036197</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -2605,10 +2605,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131752905</v>
+        <v>131752887</v>
       </c>
       <c r="B17" t="n">
-        <v>57904</v>
+        <v>83246</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2616,31 +2616,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2648,10 +2643,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>496420</v>
+        <v>496531</v>
       </c>
       <c r="R17" t="n">
-        <v>7036158</v>
+        <v>7036184</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2686,17 +2681,13 @@
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2735,10 +2726,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131752903</v>
+        <v>131752943</v>
       </c>
       <c r="B18" t="n">
-        <v>57904</v>
+        <v>80371</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2746,31 +2737,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2778,10 +2764,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496454</v>
+        <v>496214</v>
       </c>
       <c r="R18" t="n">
-        <v>7036201</v>
+        <v>7035803</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2816,17 +2802,13 @@
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2865,10 +2847,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131752943</v>
+        <v>131752905</v>
       </c>
       <c r="B19" t="n">
-        <v>80371</v>
+        <v>57904</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2876,26 +2858,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2903,10 +2890,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>496214</v>
+        <v>496420</v>
       </c>
       <c r="R19" t="n">
-        <v>7035803</v>
+        <v>7036158</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2941,13 +2928,17 @@
           <t>2026-03-18</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2986,10 +2977,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131752887</v>
+        <v>131752903</v>
       </c>
       <c r="B20" t="n">
-        <v>83246</v>
+        <v>57904</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2997,26 +2988,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3024,10 +3020,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>496531</v>
+        <v>496454</v>
       </c>
       <c r="R20" t="n">
-        <v>7036184</v>
+        <v>7036201</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3062,13 +3058,17 @@
           <t>2026-03-18</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3748,10 +3748,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131752961</v>
+        <v>131752919</v>
       </c>
       <c r="B26" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3759,26 +3759,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3786,10 +3791,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>496271</v>
+        <v>496379</v>
       </c>
       <c r="R26" t="n">
-        <v>7035921</v>
+        <v>7035973</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3826,7 +3831,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3835,7 +3840,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3854,9 +3858,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3874,10 +3883,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131752919</v>
+        <v>131752961</v>
       </c>
       <c r="B27" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3885,31 +3894,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3917,10 +3921,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>496379</v>
+        <v>496271</v>
       </c>
       <c r="R27" t="n">
-        <v>7035973</v>
+        <v>7035921</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3957,7 +3961,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3966,6 +3970,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3984,14 +3989,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4009,40 +4009,39 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131752917</v>
+        <v>131752890</v>
       </c>
       <c r="B28" t="n">
-        <v>57904</v>
+        <v>91801</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -4052,10 +4051,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>496409</v>
+        <v>496286</v>
       </c>
       <c r="R28" t="n">
-        <v>7036004</v>
+        <v>7035879</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4090,17 +4089,13 @@
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4119,14 +4114,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4144,7 +4134,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131752906</v>
+        <v>131752917</v>
       </c>
       <c r="B29" t="n">
         <v>57904</v>
@@ -4177,7 +4167,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4187,10 +4177,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>496475</v>
+        <v>496409</v>
       </c>
       <c r="R29" t="n">
-        <v>7036177</v>
+        <v>7036004</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4227,7 +4217,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4254,9 +4244,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4274,7 +4269,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131752908</v>
+        <v>131752906</v>
       </c>
       <c r="B30" t="n">
         <v>57904</v>
@@ -4317,10 +4312,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>496506</v>
+        <v>496475</v>
       </c>
       <c r="R30" t="n">
-        <v>7036124</v>
+        <v>7036177</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4404,7 +4399,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131752897</v>
+        <v>131752908</v>
       </c>
       <c r="B31" t="n">
         <v>57904</v>
@@ -4437,7 +4432,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4447,10 +4442,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>496304</v>
+        <v>496506</v>
       </c>
       <c r="R31" t="n">
-        <v>7035979</v>
+        <v>7036124</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4487,7 +4482,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4514,14 +4509,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4539,7 +4529,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131752900</v>
+        <v>131752897</v>
       </c>
       <c r="B32" t="n">
         <v>57904</v>
@@ -4582,10 +4572,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>496293</v>
+        <v>496304</v>
       </c>
       <c r="R32" t="n">
-        <v>7035993</v>
+        <v>7035979</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4674,39 +4664,40 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131752890</v>
+        <v>131752900</v>
       </c>
       <c r="B33" t="n">
-        <v>91801</v>
+        <v>57904</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4716,10 +4707,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>496286</v>
+        <v>496293</v>
       </c>
       <c r="R33" t="n">
-        <v>7035879</v>
+        <v>7035993</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4754,13 +4745,17 @@
           <t>2026-03-18</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4779,9 +4774,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>

--- a/artfynd/A 6929-2026 artfynd.xlsx
+++ b/artfynd/A 6929-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131752957</v>
       </c>
       <c r="B2" t="n">
-        <v>91858</v>
+        <v>91861</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>131752950</v>
       </c>
       <c r="B3" t="n">
-        <v>80371</v>
+        <v>80374</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>131752909</v>
       </c>
       <c r="B4" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>131752901</v>
       </c>
       <c r="B5" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1187,10 +1187,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131752891</v>
+        <v>131752962</v>
       </c>
       <c r="B6" t="n">
-        <v>91838</v>
+        <v>79269</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,30 +1198,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1229,10 +1225,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496242</v>
+        <v>496528</v>
       </c>
       <c r="R6" t="n">
-        <v>7035834</v>
+        <v>7036197</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1312,10 +1308,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131752962</v>
+        <v>131752891</v>
       </c>
       <c r="B7" t="n">
-        <v>79266</v>
+        <v>91841</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,26 +1319,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496528</v>
+        <v>496242</v>
       </c>
       <c r="R7" t="n">
-        <v>7036197</v>
+        <v>7035834</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1436,7 +1436,7 @@
         <v>131752918</v>
       </c>
       <c r="B8" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>131752915</v>
       </c>
       <c r="B9" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>131752914</v>
       </c>
       <c r="B10" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1833,10 +1833,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131752963</v>
+        <v>131752924</v>
       </c>
       <c r="B11" t="n">
-        <v>79266</v>
+        <v>57907</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1844,26 +1844,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1871,10 +1876,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>496243</v>
+        <v>496209</v>
       </c>
       <c r="R11" t="n">
-        <v>7035811</v>
+        <v>7035774</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1911,7 +1916,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1920,7 +1925,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1939,9 +1943,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1959,10 +1968,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131752924</v>
+        <v>131752910</v>
       </c>
       <c r="B12" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1992,7 +2001,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2002,10 +2011,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>496209</v>
+        <v>496471</v>
       </c>
       <c r="R12" t="n">
-        <v>7035774</v>
+        <v>7036080</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2042,7 +2051,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2069,14 +2078,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2094,10 +2098,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131752910</v>
+        <v>131752963</v>
       </c>
       <c r="B13" t="n">
-        <v>57904</v>
+        <v>79269</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2105,31 +2109,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2137,10 +2136,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>496471</v>
+        <v>496243</v>
       </c>
       <c r="R13" t="n">
-        <v>7036080</v>
+        <v>7035811</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2177,7 +2176,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2186,6 +2185,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2227,7 +2227,7 @@
         <v>131752913</v>
       </c>
       <c r="B14" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>131752923</v>
       </c>
       <c r="B15" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>131752956</v>
       </c>
       <c r="B16" t="n">
-        <v>91858</v>
+        <v>91861</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>131752887</v>
       </c>
       <c r="B17" t="n">
-        <v>83246</v>
+        <v>83249</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>131752943</v>
       </c>
       <c r="B18" t="n">
-        <v>80371</v>
+        <v>80374</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>131752905</v>
       </c>
       <c r="B19" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>131752903</v>
       </c>
       <c r="B20" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>131752920</v>
       </c>
       <c r="B21" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>131752955</v>
       </c>
       <c r="B22" t="n">
-        <v>91834</v>
+        <v>91837</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3362,10 +3362,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131752898</v>
+        <v>131752942</v>
       </c>
       <c r="B23" t="n">
-        <v>57904</v>
+        <v>80375</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3373,31 +3373,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3405,10 +3400,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496293</v>
+        <v>496194</v>
       </c>
       <c r="R23" t="n">
-        <v>7035984</v>
+        <v>7035755</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3443,17 +3438,13 @@
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3464,22 +3455,17 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3497,10 +3483,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131752907</v>
+        <v>131752898</v>
       </c>
       <c r="B24" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3530,7 +3516,7 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3540,10 +3526,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>496513</v>
+        <v>496293</v>
       </c>
       <c r="R24" t="n">
-        <v>7036129</v>
+        <v>7035984</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3580,7 +3566,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3607,9 +3593,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3627,10 +3618,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131752942</v>
+        <v>131752907</v>
       </c>
       <c r="B25" t="n">
-        <v>80372</v>
+        <v>57907</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3638,26 +3629,31 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3665,10 +3661,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>496194</v>
+        <v>496513</v>
       </c>
       <c r="R25" t="n">
-        <v>7035755</v>
+        <v>7036129</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3703,13 +3699,17 @@
           <t>2026-03-18</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3720,17 +3720,17 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3748,10 +3748,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131752919</v>
+        <v>131752961</v>
       </c>
       <c r="B26" t="n">
-        <v>57904</v>
+        <v>79269</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3759,31 +3759,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3791,10 +3786,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>496379</v>
+        <v>496271</v>
       </c>
       <c r="R26" t="n">
-        <v>7035973</v>
+        <v>7035921</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3831,7 +3826,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3840,6 +3835,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3858,14 +3854,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3883,10 +3874,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131752961</v>
+        <v>131752919</v>
       </c>
       <c r="B27" t="n">
-        <v>79266</v>
+        <v>57907</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3894,26 +3885,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3921,10 +3917,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>496271</v>
+        <v>496379</v>
       </c>
       <c r="R27" t="n">
-        <v>7035921</v>
+        <v>7035973</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3961,7 +3957,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3970,7 +3966,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3989,9 +3984,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4012,7 +4012,7 @@
         <v>131752890</v>
       </c>
       <c r="B28" t="n">
-        <v>91801</v>
+        <v>91804</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4137,7 +4137,7 @@
         <v>131752917</v>
       </c>
       <c r="B29" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>131752906</v>
       </c>
       <c r="B30" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         <v>131752908</v>
       </c>
       <c r="B31" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>131752897</v>
       </c>
       <c r="B32" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>131752900</v>
       </c>
       <c r="B33" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
         <v>131752922</v>
       </c>
       <c r="B34" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>131752911</v>
       </c>
       <c r="B35" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5064,10 +5064,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131752953</v>
+        <v>131752949</v>
       </c>
       <c r="B36" t="n">
-        <v>78278</v>
+        <v>80374</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5075,21 +5075,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -5102,10 +5102,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>496536</v>
+        <v>496198</v>
       </c>
       <c r="R36" t="n">
-        <v>7036191</v>
+        <v>7035790</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5157,17 +5157,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5185,10 +5190,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131752949</v>
+        <v>131752953</v>
       </c>
       <c r="B37" t="n">
-        <v>80371</v>
+        <v>78281</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5196,21 +5201,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5223,10 +5228,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>496198</v>
+        <v>496536</v>
       </c>
       <c r="R37" t="n">
-        <v>7035790</v>
+        <v>7036191</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5278,22 +5283,17 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5314,7 +5314,7 @@
         <v>131752944</v>
       </c>
       <c r="B38" t="n">
-        <v>80371</v>
+        <v>80374</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131752939</v>
+        <v>131752896</v>
       </c>
       <c r="B39" t="n">
-        <v>80372</v>
+        <v>57907</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5443,26 +5443,31 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5470,10 +5475,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>496130</v>
+        <v>496249</v>
       </c>
       <c r="R39" t="n">
-        <v>7035728</v>
+        <v>7035881</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5508,13 +5513,17 @@
           <t>2026-03-18</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en tall.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5525,22 +5534,17 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5558,10 +5562,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131752896</v>
+        <v>131752939</v>
       </c>
       <c r="B40" t="n">
-        <v>57904</v>
+        <v>80375</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5569,31 +5573,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5601,10 +5600,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>496249</v>
+        <v>496130</v>
       </c>
       <c r="R40" t="n">
-        <v>7035881</v>
+        <v>7035728</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5639,17 +5638,13 @@
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en tall.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5660,17 +5655,22 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5691,7 +5691,7 @@
         <v>131752912</v>
       </c>
       <c r="B41" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5821,7 +5821,7 @@
         <v>131752902</v>
       </c>
       <c r="B42" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>131752941</v>
       </c>
       <c r="B43" t="n">
-        <v>80372</v>
+        <v>80375</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>131752958</v>
       </c>
       <c r="B44" t="n">
-        <v>91858</v>
+        <v>91861</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>131752952</v>
       </c>
       <c r="B45" t="n">
-        <v>80371</v>
+        <v>80374</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6329,7 +6329,7 @@
         <v>131752947</v>
       </c>
       <c r="B46" t="n">
-        <v>80371</v>
+        <v>80374</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         <v>131752946</v>
       </c>
       <c r="B47" t="n">
-        <v>80371</v>
+        <v>80374</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>131752916</v>
       </c>
       <c r="B48" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         <v>131752938</v>
       </c>
       <c r="B49" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
         <v>131752945</v>
       </c>
       <c r="B50" t="n">
-        <v>80371</v>
+        <v>80374</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6962,7 +6962,7 @@
         <v>131752940</v>
       </c>
       <c r="B51" t="n">
-        <v>80372</v>
+        <v>80375</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7083,7 +7083,7 @@
         <v>131752951</v>
       </c>
       <c r="B52" t="n">
-        <v>80371</v>
+        <v>80374</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>131752904</v>
       </c>
       <c r="B53" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 6929-2026 artfynd.xlsx
+++ b/artfynd/A 6929-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131752957</v>
       </c>
       <c r="B2" t="n">
-        <v>91861</v>
+        <v>91866</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>131752950</v>
       </c>
       <c r="B3" t="n">
-        <v>80374</v>
+        <v>80379</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>131752909</v>
       </c>
       <c r="B4" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>131752901</v>
       </c>
       <c r="B5" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1187,10 +1187,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131752962</v>
+        <v>131752891</v>
       </c>
       <c r="B6" t="n">
-        <v>79269</v>
+        <v>91846</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,26 +1198,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1225,10 +1229,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496528</v>
+        <v>496242</v>
       </c>
       <c r="R6" t="n">
-        <v>7036197</v>
+        <v>7035834</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1308,10 +1312,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131752891</v>
+        <v>131752962</v>
       </c>
       <c r="B7" t="n">
-        <v>91841</v>
+        <v>79274</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,30 +1323,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496242</v>
+        <v>496528</v>
       </c>
       <c r="R7" t="n">
-        <v>7035834</v>
+        <v>7036197</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1436,7 +1436,7 @@
         <v>131752918</v>
       </c>
       <c r="B8" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>131752915</v>
       </c>
       <c r="B9" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>131752914</v>
       </c>
       <c r="B10" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1833,10 +1833,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131752924</v>
+        <v>131752963</v>
       </c>
       <c r="B11" t="n">
-        <v>57907</v>
+        <v>79274</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1844,31 +1844,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1876,10 +1871,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>496209</v>
+        <v>496243</v>
       </c>
       <c r="R11" t="n">
-        <v>7035774</v>
+        <v>7035811</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1916,7 +1911,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1925,6 +1920,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1943,14 +1939,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1968,10 +1959,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131752910</v>
+        <v>131752924</v>
       </c>
       <c r="B12" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2001,7 +1992,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2011,10 +2002,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>496471</v>
+        <v>496209</v>
       </c>
       <c r="R12" t="n">
-        <v>7036080</v>
+        <v>7035774</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2051,7 +2042,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2078,9 +2069,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2098,10 +2094,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131752963</v>
+        <v>131752910</v>
       </c>
       <c r="B13" t="n">
-        <v>79269</v>
+        <v>57912</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2109,26 +2105,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2136,10 +2137,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>496243</v>
+        <v>496471</v>
       </c>
       <c r="R13" t="n">
-        <v>7035811</v>
+        <v>7036080</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2176,7 +2177,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2185,7 +2186,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2227,7 +2227,7 @@
         <v>131752913</v>
       </c>
       <c r="B14" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>131752923</v>
       </c>
       <c r="B15" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>131752956</v>
       </c>
       <c r="B16" t="n">
-        <v>91861</v>
+        <v>91866</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>131752887</v>
       </c>
       <c r="B17" t="n">
-        <v>83249</v>
+        <v>83254</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>131752943</v>
       </c>
       <c r="B18" t="n">
-        <v>80374</v>
+        <v>80379</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>131752905</v>
       </c>
       <c r="B19" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>131752903</v>
       </c>
       <c r="B20" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3107,10 +3107,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131752920</v>
+        <v>131752955</v>
       </c>
       <c r="B21" t="n">
-        <v>57907</v>
+        <v>91842</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3118,29 +3118,28 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3150,10 +3149,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>496360</v>
+        <v>496475</v>
       </c>
       <c r="R21" t="n">
-        <v>7035948</v>
+        <v>7036170</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3188,17 +3187,13 @@
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3237,10 +3232,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131752955</v>
+        <v>131752920</v>
       </c>
       <c r="B22" t="n">
-        <v>91837</v>
+        <v>57912</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3248,28 +3243,29 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3279,10 +3275,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496475</v>
+        <v>496360</v>
       </c>
       <c r="R22" t="n">
-        <v>7036170</v>
+        <v>7035948</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3317,13 +3313,17 @@
           <t>2026-03-18</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3365,7 +3365,7 @@
         <v>131752942</v>
       </c>
       <c r="B23" t="n">
-        <v>80375</v>
+        <v>80380</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>131752898</v>
       </c>
       <c r="B24" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>131752907</v>
       </c>
       <c r="B25" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>131752961</v>
       </c>
       <c r="B26" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>131752919</v>
       </c>
       <c r="B27" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4012,7 +4012,7 @@
         <v>131752890</v>
       </c>
       <c r="B28" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4137,7 +4137,7 @@
         <v>131752917</v>
       </c>
       <c r="B29" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>131752906</v>
       </c>
       <c r="B30" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         <v>131752908</v>
       </c>
       <c r="B31" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>131752897</v>
       </c>
       <c r="B32" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>131752900</v>
       </c>
       <c r="B33" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
         <v>131752922</v>
       </c>
       <c r="B34" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>131752911</v>
       </c>
       <c r="B35" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>131752949</v>
       </c>
       <c r="B36" t="n">
-        <v>80374</v>
+        <v>80379</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>131752953</v>
       </c>
       <c r="B37" t="n">
-        <v>78281</v>
+        <v>78286</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>131752944</v>
       </c>
       <c r="B38" t="n">
-        <v>80374</v>
+        <v>80379</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131752896</v>
+        <v>131752939</v>
       </c>
       <c r="B39" t="n">
-        <v>57907</v>
+        <v>80380</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5443,31 +5443,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5475,10 +5470,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>496249</v>
+        <v>496130</v>
       </c>
       <c r="R39" t="n">
-        <v>7035881</v>
+        <v>7035728</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5513,17 +5508,13 @@
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en tall.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5534,17 +5525,22 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5562,10 +5558,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131752939</v>
+        <v>131752896</v>
       </c>
       <c r="B40" t="n">
-        <v>80375</v>
+        <v>57912</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5573,26 +5569,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5600,10 +5601,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>496130</v>
+        <v>496249</v>
       </c>
       <c r="R40" t="n">
-        <v>7035728</v>
+        <v>7035881</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5638,13 +5639,17 @@
           <t>2026-03-18</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en tall.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5655,22 +5660,17 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5691,7 +5691,7 @@
         <v>131752912</v>
       </c>
       <c r="B41" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5821,7 +5821,7 @@
         <v>131752902</v>
       </c>
       <c r="B42" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5953,10 +5953,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131752941</v>
+        <v>131752958</v>
       </c>
       <c r="B43" t="n">
-        <v>80375</v>
+        <v>91866</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5964,26 +5964,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5991,10 +5991,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>496195</v>
+        <v>496359</v>
       </c>
       <c r="R43" t="n">
-        <v>7035791</v>
+        <v>7035980</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6046,22 +6046,17 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6079,10 +6074,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131752958</v>
+        <v>131752941</v>
       </c>
       <c r="B44" t="n">
-        <v>91861</v>
+        <v>80380</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6090,26 +6085,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -6117,10 +6112,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>496359</v>
+        <v>496195</v>
       </c>
       <c r="R44" t="n">
-        <v>7035980</v>
+        <v>7035791</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6172,17 +6167,22 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6203,7 +6203,7 @@
         <v>131752952</v>
       </c>
       <c r="B45" t="n">
-        <v>80374</v>
+        <v>80379</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6329,7 +6329,7 @@
         <v>131752947</v>
       </c>
       <c r="B46" t="n">
-        <v>80374</v>
+        <v>80379</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         <v>131752946</v>
       </c>
       <c r="B47" t="n">
-        <v>80374</v>
+        <v>80379</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>131752916</v>
       </c>
       <c r="B48" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         <v>131752938</v>
       </c>
       <c r="B49" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
         <v>131752945</v>
       </c>
       <c r="B50" t="n">
-        <v>80374</v>
+        <v>80379</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6962,7 +6962,7 @@
         <v>131752940</v>
       </c>
       <c r="B51" t="n">
-        <v>80375</v>
+        <v>80380</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7083,7 +7083,7 @@
         <v>131752951</v>
       </c>
       <c r="B52" t="n">
-        <v>80374</v>
+        <v>80379</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>131752904</v>
       </c>
       <c r="B53" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 6929-2026 artfynd.xlsx
+++ b/artfynd/A 6929-2026 artfynd.xlsx
@@ -3748,10 +3748,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131752961</v>
+        <v>131752919</v>
       </c>
       <c r="B26" t="n">
-        <v>79274</v>
+        <v>57912</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3759,26 +3759,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3786,10 +3791,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>496271</v>
+        <v>496379</v>
       </c>
       <c r="R26" t="n">
-        <v>7035921</v>
+        <v>7035973</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3826,7 +3831,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3835,7 +3840,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3854,9 +3858,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3874,10 +3883,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131752919</v>
+        <v>131752961</v>
       </c>
       <c r="B27" t="n">
-        <v>57912</v>
+        <v>79274</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3885,31 +3894,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3917,10 +3921,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>496379</v>
+        <v>496271</v>
       </c>
       <c r="R27" t="n">
-        <v>7035973</v>
+        <v>7035921</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3957,7 +3961,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3966,6 +3970,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3984,14 +3989,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -5311,10 +5311,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131752944</v>
+        <v>131752939</v>
       </c>
       <c r="B38" t="n">
-        <v>80379</v>
+        <v>80380</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5322,21 +5322,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5349,10 +5349,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>496246</v>
+        <v>496130</v>
       </c>
       <c r="R38" t="n">
-        <v>7035859</v>
+        <v>7035728</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5412,9 +5412,14 @@
           <t>Salix caprea</t>
         </is>
       </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5432,10 +5437,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131752939</v>
+        <v>131752896</v>
       </c>
       <c r="B39" t="n">
-        <v>80380</v>
+        <v>57912</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5443,26 +5448,31 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5470,10 +5480,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>496130</v>
+        <v>496249</v>
       </c>
       <c r="R39" t="n">
-        <v>7035728</v>
+        <v>7035881</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5508,13 +5518,17 @@
           <t>2026-03-18</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en tall.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5525,22 +5539,17 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5558,10 +5567,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131752896</v>
+        <v>131752944</v>
       </c>
       <c r="B40" t="n">
-        <v>57912</v>
+        <v>80379</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5569,31 +5578,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5601,10 +5605,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>496249</v>
+        <v>496246</v>
       </c>
       <c r="R40" t="n">
-        <v>7035881</v>
+        <v>7035859</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5639,17 +5643,13 @@
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en tall.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5660,17 +5660,17 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -6838,10 +6838,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131752945</v>
+        <v>131752940</v>
       </c>
       <c r="B50" t="n">
-        <v>80379</v>
+        <v>80380</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6849,21 +6849,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6876,10 +6876,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>496358</v>
+        <v>496212</v>
       </c>
       <c r="R50" t="n">
-        <v>7035946</v>
+        <v>7035799</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6959,10 +6959,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131752940</v>
+        <v>131752945</v>
       </c>
       <c r="B51" t="n">
-        <v>80380</v>
+        <v>80379</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6970,21 +6970,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6997,10 +6997,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>496212</v>
+        <v>496358</v>
       </c>
       <c r="R51" t="n">
-        <v>7035799</v>
+        <v>7035946</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>

--- a/artfynd/A 6929-2026 artfynd.xlsx
+++ b/artfynd/A 6929-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131752957</v>
+        <v>131752950</v>
       </c>
       <c r="B2" t="n">
-        <v>91866</v>
+        <v>80381</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,26 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>496342</v>
+        <v>496205</v>
       </c>
       <c r="R2" t="n">
-        <v>7036007</v>
+        <v>7035804</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -768,17 +768,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -796,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131752950</v>
+        <v>131752909</v>
       </c>
       <c r="B3" t="n">
-        <v>80379</v>
+        <v>57914</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,26 +812,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496205</v>
+        <v>496478</v>
       </c>
       <c r="R3" t="n">
-        <v>7035804</v>
+        <v>7036088</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,13 +882,17 @@
           <t>2026-03-18</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -889,22 +903,17 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -922,10 +931,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131752909</v>
+        <v>131752901</v>
       </c>
       <c r="B4" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -955,7 +964,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -965,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496478</v>
+        <v>496305</v>
       </c>
       <c r="R4" t="n">
-        <v>7036088</v>
+        <v>7036020</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,7 +1014,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,9 +1041,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1052,10 +1066,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131752901</v>
+        <v>131752957</v>
       </c>
       <c r="B5" t="n">
-        <v>57912</v>
+        <v>91868</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,29 +1077,24 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1095,10 +1104,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>496305</v>
+        <v>496342</v>
       </c>
       <c r="R5" t="n">
-        <v>7036020</v>
+        <v>7036007</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1133,17 +1142,13 @@
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1162,14 +1167,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1187,10 +1187,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131752891</v>
+        <v>131752962</v>
       </c>
       <c r="B6" t="n">
-        <v>91846</v>
+        <v>79276</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,30 +1198,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1229,10 +1225,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496242</v>
+        <v>496528</v>
       </c>
       <c r="R6" t="n">
-        <v>7035834</v>
+        <v>7036197</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1312,10 +1308,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131752962</v>
+        <v>131752891</v>
       </c>
       <c r="B7" t="n">
-        <v>79274</v>
+        <v>91848</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,26 +1319,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496528</v>
+        <v>496242</v>
       </c>
       <c r="R7" t="n">
-        <v>7036197</v>
+        <v>7035834</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1433,10 +1433,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131752918</v>
+        <v>131752915</v>
       </c>
       <c r="B8" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,10 +1476,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496408</v>
+        <v>496426</v>
       </c>
       <c r="R8" t="n">
-        <v>7036004</v>
+        <v>7036022</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1568,10 +1568,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131752915</v>
+        <v>131752914</v>
       </c>
       <c r="B9" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496426</v>
+        <v>496424</v>
       </c>
       <c r="R9" t="n">
-        <v>7036022</v>
+        <v>7036021</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1678,14 +1678,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1703,10 +1698,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131752914</v>
+        <v>131752918</v>
       </c>
       <c r="B10" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1746,10 +1741,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>496424</v>
+        <v>496408</v>
       </c>
       <c r="R10" t="n">
-        <v>7036021</v>
+        <v>7036004</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1813,9 +1808,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1833,10 +1833,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131752963</v>
+        <v>131752910</v>
       </c>
       <c r="B11" t="n">
-        <v>79274</v>
+        <v>57914</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1844,26 +1844,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1871,10 +1876,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>496243</v>
+        <v>496471</v>
       </c>
       <c r="R11" t="n">
-        <v>7035811</v>
+        <v>7036080</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1911,7 +1916,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1920,7 +1925,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1959,10 +1963,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131752924</v>
+        <v>131752963</v>
       </c>
       <c r="B12" t="n">
-        <v>57912</v>
+        <v>79276</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1970,31 +1974,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2002,10 +2001,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>496209</v>
+        <v>496243</v>
       </c>
       <c r="R12" t="n">
-        <v>7035774</v>
+        <v>7035811</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2042,7 +2041,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2051,6 +2050,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2069,14 +2069,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2094,10 +2089,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131752910</v>
+        <v>131752924</v>
       </c>
       <c r="B13" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2127,7 +2122,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2137,10 +2132,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>496471</v>
+        <v>496209</v>
       </c>
       <c r="R13" t="n">
-        <v>7036080</v>
+        <v>7035774</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2177,7 +2172,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2204,9 +2199,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2224,10 +2224,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131752913</v>
+        <v>131752923</v>
       </c>
       <c r="B14" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>496421</v>
+        <v>496335</v>
       </c>
       <c r="R14" t="n">
-        <v>7036017</v>
+        <v>7035918</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2354,10 +2354,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131752923</v>
+        <v>131752913</v>
       </c>
       <c r="B15" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2397,10 +2397,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>496335</v>
+        <v>496421</v>
       </c>
       <c r="R15" t="n">
-        <v>7035918</v>
+        <v>7036017</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2484,10 +2484,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131752956</v>
+        <v>131752887</v>
       </c>
       <c r="B16" t="n">
-        <v>91866</v>
+        <v>83256</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2495,26 +2495,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2522,10 +2522,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>496130</v>
+        <v>496531</v>
       </c>
       <c r="R16" t="n">
-        <v>7035766</v>
+        <v>7036184</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2605,10 +2605,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131752887</v>
+        <v>131752943</v>
       </c>
       <c r="B17" t="n">
-        <v>83254</v>
+        <v>80381</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2616,21 +2616,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>496531</v>
+        <v>496214</v>
       </c>
       <c r="R17" t="n">
-        <v>7036184</v>
+        <v>7035803</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2726,10 +2726,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131752943</v>
+        <v>131752956</v>
       </c>
       <c r="B18" t="n">
-        <v>80379</v>
+        <v>91868</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2737,26 +2737,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496214</v>
+        <v>496130</v>
       </c>
       <c r="R18" t="n">
-        <v>7035803</v>
+        <v>7035766</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2850,7 +2850,7 @@
         <v>131752905</v>
       </c>
       <c r="B19" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>131752903</v>
       </c>
       <c r="B20" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>131752955</v>
       </c>
       <c r="B21" t="n">
-        <v>91842</v>
+        <v>91844</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>131752920</v>
       </c>
       <c r="B22" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3362,10 +3362,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131752942</v>
+        <v>131752898</v>
       </c>
       <c r="B23" t="n">
-        <v>80380</v>
+        <v>57914</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3373,26 +3373,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3400,10 +3405,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496194</v>
+        <v>496293</v>
       </c>
       <c r="R23" t="n">
-        <v>7035755</v>
+        <v>7035984</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3438,13 +3443,17 @@
           <t>2026-03-18</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3455,17 +3464,22 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3483,10 +3497,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131752898</v>
+        <v>131752942</v>
       </c>
       <c r="B24" t="n">
-        <v>57912</v>
+        <v>80382</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3494,31 +3508,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3526,10 +3535,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>496293</v>
+        <v>496194</v>
       </c>
       <c r="R24" t="n">
-        <v>7035984</v>
+        <v>7035755</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3564,17 +3573,13 @@
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3585,22 +3590,17 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3621,7 +3621,7 @@
         <v>131752907</v>
       </c>
       <c r="B25" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3748,10 +3748,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131752919</v>
+        <v>131752961</v>
       </c>
       <c r="B26" t="n">
-        <v>57912</v>
+        <v>79276</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3759,31 +3759,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3791,10 +3786,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>496379</v>
+        <v>496271</v>
       </c>
       <c r="R26" t="n">
-        <v>7035973</v>
+        <v>7035921</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3831,7 +3826,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3840,6 +3835,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3858,14 +3854,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3883,10 +3874,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131752961</v>
+        <v>131752919</v>
       </c>
       <c r="B27" t="n">
-        <v>79274</v>
+        <v>57914</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3894,26 +3885,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3921,10 +3917,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>496271</v>
+        <v>496379</v>
       </c>
       <c r="R27" t="n">
-        <v>7035921</v>
+        <v>7035973</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3961,7 +3957,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3970,7 +3966,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3989,9 +3984,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4012,7 +4012,7 @@
         <v>131752890</v>
       </c>
       <c r="B28" t="n">
-        <v>91809</v>
+        <v>91811</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131752917</v>
+        <v>131752906</v>
       </c>
       <c r="B29" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4177,10 +4177,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>496409</v>
+        <v>496475</v>
       </c>
       <c r="R29" t="n">
-        <v>7036004</v>
+        <v>7036177</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4217,7 +4217,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4244,14 +4244,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4269,10 +4264,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131752906</v>
+        <v>131752908</v>
       </c>
       <c r="B30" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4312,10 +4307,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>496475</v>
+        <v>496506</v>
       </c>
       <c r="R30" t="n">
-        <v>7036177</v>
+        <v>7036124</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4399,10 +4394,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131752908</v>
+        <v>131752917</v>
       </c>
       <c r="B31" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4432,7 +4427,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4442,10 +4437,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>496506</v>
+        <v>496409</v>
       </c>
       <c r="R31" t="n">
-        <v>7036124</v>
+        <v>7036004</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4482,7 +4477,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4509,9 +4504,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4532,7 +4532,7 @@
         <v>131752897</v>
       </c>
       <c r="B32" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>131752900</v>
       </c>
       <c r="B33" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4799,10 +4799,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131752922</v>
+        <v>131752911</v>
       </c>
       <c r="B34" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4842,10 +4842,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>496323</v>
+        <v>496472</v>
       </c>
       <c r="R34" t="n">
-        <v>7035905</v>
+        <v>7036081</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4882,7 +4882,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4909,9 +4909,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4929,10 +4934,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131752911</v>
+        <v>131752922</v>
       </c>
       <c r="B35" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4962,7 +4967,7 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -4972,10 +4977,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>496472</v>
+        <v>496323</v>
       </c>
       <c r="R35" t="n">
-        <v>7036081</v>
+        <v>7035905</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5012,7 +5017,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5039,14 +5044,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5067,7 +5067,7 @@
         <v>131752949</v>
       </c>
       <c r="B36" t="n">
-        <v>80379</v>
+        <v>80381</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>131752953</v>
       </c>
       <c r="B37" t="n">
-        <v>78286</v>
+        <v>78288</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5311,10 +5311,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131752939</v>
+        <v>131752944</v>
       </c>
       <c r="B38" t="n">
-        <v>80380</v>
+        <v>80381</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5322,21 +5322,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5349,10 +5349,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>496130</v>
+        <v>496246</v>
       </c>
       <c r="R38" t="n">
-        <v>7035728</v>
+        <v>7035859</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5412,14 +5412,9 @@
           <t>Salix caprea</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5437,10 +5432,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131752896</v>
+        <v>131752939</v>
       </c>
       <c r="B39" t="n">
-        <v>57912</v>
+        <v>80382</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5448,31 +5443,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5480,10 +5470,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>496249</v>
+        <v>496130</v>
       </c>
       <c r="R39" t="n">
-        <v>7035881</v>
+        <v>7035728</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5518,17 +5508,13 @@
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en tall.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5539,17 +5525,22 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5567,10 +5558,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131752944</v>
+        <v>131752896</v>
       </c>
       <c r="B40" t="n">
-        <v>80379</v>
+        <v>57914</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5578,26 +5569,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5605,10 +5601,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>496246</v>
+        <v>496249</v>
       </c>
       <c r="R40" t="n">
-        <v>7035859</v>
+        <v>7035881</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5643,13 +5639,17 @@
           <t>2026-03-18</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en tall.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5660,17 +5660,17 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5691,7 +5691,7 @@
         <v>131752912</v>
       </c>
       <c r="B41" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5821,7 +5821,7 @@
         <v>131752902</v>
       </c>
       <c r="B42" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5953,10 +5953,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131752958</v>
+        <v>131752941</v>
       </c>
       <c r="B43" t="n">
-        <v>91866</v>
+        <v>80382</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5964,26 +5964,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5991,10 +5991,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>496359</v>
+        <v>496195</v>
       </c>
       <c r="R43" t="n">
-        <v>7035980</v>
+        <v>7035791</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6046,17 +6046,22 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6074,10 +6079,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131752941</v>
+        <v>131752958</v>
       </c>
       <c r="B44" t="n">
-        <v>80380</v>
+        <v>91868</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6085,26 +6090,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -6112,10 +6117,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>496195</v>
+        <v>496359</v>
       </c>
       <c r="R44" t="n">
-        <v>7035791</v>
+        <v>7035980</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6167,22 +6172,17 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6203,7 +6203,7 @@
         <v>131752952</v>
       </c>
       <c r="B45" t="n">
-        <v>80379</v>
+        <v>80381</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6329,7 +6329,7 @@
         <v>131752947</v>
       </c>
       <c r="B46" t="n">
-        <v>80379</v>
+        <v>80381</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         <v>131752946</v>
       </c>
       <c r="B47" t="n">
-        <v>80379</v>
+        <v>80381</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131752916</v>
+        <v>131752938</v>
       </c>
       <c r="B48" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6606,7 +6606,7 @@
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -6616,10 +6616,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>496424</v>
+        <v>496294</v>
       </c>
       <c r="R48" t="n">
-        <v>7036028</v>
+        <v>7035996</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6656,7 +6656,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6683,9 +6683,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6703,10 +6708,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131752938</v>
+        <v>131752916</v>
       </c>
       <c r="B49" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6736,7 +6741,7 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -6746,10 +6751,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>496294</v>
+        <v>496424</v>
       </c>
       <c r="R49" t="n">
-        <v>7035996</v>
+        <v>7036028</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6786,7 +6791,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6813,14 +6818,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6841,7 +6841,7 @@
         <v>131752940</v>
       </c>
       <c r="B50" t="n">
-        <v>80380</v>
+        <v>80382</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6962,7 +6962,7 @@
         <v>131752945</v>
       </c>
       <c r="B51" t="n">
-        <v>80379</v>
+        <v>80381</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7083,7 +7083,7 @@
         <v>131752951</v>
       </c>
       <c r="B52" t="n">
-        <v>80379</v>
+        <v>80381</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>131752904</v>
       </c>
       <c r="B53" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
